--- a/course-design-2/outputs/tables/ch7/52_stage26_4_metrics_final.xlsx
+++ b/course-design-2/outputs/tables/ch7/52_stage26_4_metrics_final.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_三种划分统一协议" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_消融五配置" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_消融增量bootstrap" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_模型比较" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_最终模型测试集" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_分组预测误差四分位" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_岗位大类预测误差" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_多种子明细" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_多种子汇总" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_公司分组多次划分" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_公司分组汇总" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_稳健性对照" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_主模型SHAP特征" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_技能SHAP" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_图4-4新旧数据对照" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet name="01_三种划分统一协议" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet name="02_消融五配置" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet name="03_消融增量bootstrap" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet name="04_模型比较" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet name="05_最终模型测试集" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet name="06_分组预测误差四分位" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet name="07_岗位大类预测误差" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet name="08_多种子明细" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet name="09_多种子汇总" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet name="10_公司分组多次划分" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet name="11_公司分组汇总" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet name="12_稳健性对照" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet name="13_主模型SHAP特征" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet name="14_技能SHAP" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet name="15_图4-4新旧数据对照" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,31 +546,31 @@
         <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>35.996481</v>
+        <v>36.453256</v>
       </c>
       <c r="H2" t="n">
-        <v>66.29566699999999</v>
+        <v>67.24848</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5628300000000001</v>
+        <v>0.5501740000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>36.038993</v>
+        <v>36.635124</v>
       </c>
       <c r="K2" t="n">
-        <v>69.9654</v>
+        <v>70.771012</v>
       </c>
       <c r="L2" t="n">
-        <v>0.588565</v>
+        <v>0.579035</v>
       </c>
       <c r="M2" t="n">
-        <v>36.451863</v>
+        <v>36.354494</v>
       </c>
       <c r="N2" t="n">
-        <v>66.85369900000001</v>
+        <v>67.36623</v>
       </c>
       <c r="O2" t="n">
-        <v>0.55544</v>
+        <v>0.548597</v>
       </c>
       <c r="P2" t="n">
         <v>308</v>
@@ -598,31 +598,31 @@
         <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>51.983919</v>
+        <v>52.794804</v>
       </c>
       <c r="H3" t="n">
-        <v>103.57182</v>
+        <v>104.800307</v>
       </c>
       <c r="I3" t="n">
-        <v>0.135892</v>
+        <v>0.115272</v>
       </c>
       <c r="J3" t="n">
-        <v>56.723294</v>
+        <v>56.773993</v>
       </c>
       <c r="K3" t="n">
-        <v>100.257122</v>
+        <v>99.90326399999999</v>
       </c>
       <c r="L3" t="n">
-        <v>0.137079</v>
+        <v>0.143159</v>
       </c>
       <c r="M3" t="n">
-        <v>52.093534</v>
+        <v>51.629921</v>
       </c>
       <c r="N3" t="n">
-        <v>103.691486</v>
+        <v>103.613495</v>
       </c>
       <c r="O3" t="n">
-        <v>0.133895</v>
+        <v>0.135197</v>
       </c>
       <c r="P3" t="n">
         <v>299</v>
@@ -650,31 +650,31 @@
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>31.719235</v>
+        <v>31.818072</v>
       </c>
       <c r="H4" t="n">
-        <v>47.615814</v>
+        <v>47.694496</v>
       </c>
       <c r="I4" t="n">
-        <v>0.6563099999999999</v>
+        <v>0.655173</v>
       </c>
       <c r="J4" t="n">
-        <v>38.853433</v>
+        <v>39.323111</v>
       </c>
       <c r="K4" t="n">
-        <v>72.325975</v>
+        <v>72.798478</v>
       </c>
       <c r="L4" t="n">
-        <v>0.508782</v>
+        <v>0.502343</v>
       </c>
       <c r="M4" t="n">
-        <v>32.132572</v>
+        <v>31.858455</v>
       </c>
       <c r="N4" t="n">
-        <v>47.817303</v>
+        <v>48.03658</v>
       </c>
       <c r="O4" t="n">
-        <v>0.6533949999999999</v>
+        <v>0.650209</v>
       </c>
       <c r="P4" t="n">
         <v>309</v>
@@ -753,13 +753,13 @@
         <v>1688</v>
       </c>
       <c r="F2" t="n">
-        <v>51.983919</v>
+        <v>52.794804</v>
       </c>
       <c r="G2" t="n">
-        <v>103.57182</v>
+        <v>104.800307</v>
       </c>
       <c r="H2" t="n">
-        <v>0.135892</v>
+        <v>0.115272</v>
       </c>
     </row>
     <row r="3">
@@ -779,13 +779,13 @@
         <v>2842</v>
       </c>
       <c r="F3" t="n">
-        <v>81.46315</v>
+        <v>80.844548</v>
       </c>
       <c r="G3" t="n">
-        <v>121.563886</v>
+        <v>120.154008</v>
       </c>
       <c r="H3" t="n">
-        <v>0.018063</v>
+        <v>0.040708</v>
       </c>
     </row>
     <row r="4">
@@ -805,13 +805,13 @@
         <v>1988</v>
       </c>
       <c r="F4" t="n">
-        <v>38.831912</v>
+        <v>38.738047</v>
       </c>
       <c r="G4" t="n">
-        <v>62.099138</v>
+        <v>61.774548</v>
       </c>
       <c r="H4" t="n">
-        <v>0.146623</v>
+        <v>0.155521</v>
       </c>
     </row>
     <row r="5">
@@ -831,13 +831,13 @@
         <v>1867</v>
       </c>
       <c r="F5" t="n">
-        <v>49.441596</v>
+        <v>48.936058</v>
       </c>
       <c r="G5" t="n">
-        <v>101.740059</v>
+        <v>101.608421</v>
       </c>
       <c r="H5" t="n">
-        <v>0.116458</v>
+        <v>0.118743</v>
       </c>
     </row>
     <row r="6">
@@ -857,13 +857,13 @@
         <v>1870</v>
       </c>
       <c r="F6" t="n">
-        <v>45.73755</v>
+        <v>45.683421</v>
       </c>
       <c r="G6" t="n">
-        <v>79.59930300000001</v>
+        <v>79.04685600000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.089715</v>
+        <v>0.102307</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53.491625</v>
+        <v>53.399376</v>
       </c>
     </row>
     <row r="3">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.402096</v>
+        <v>16.186528</v>
       </c>
     </row>
     <row r="4">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.831912</v>
+        <v>38.738047</v>
       </c>
     </row>
     <row r="5">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>81.46315</v>
+        <v>80.844548</v>
       </c>
     </row>
     <row r="6">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93.71484100000001</v>
+        <v>93.476828</v>
       </c>
     </row>
     <row r="7">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.108086</v>
+        <v>23.01779</v>
       </c>
     </row>
     <row r="8">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.10135</v>
+        <v>0.10651</v>
       </c>
     </row>
     <row r="9">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.05134</v>
+        <v>0.041761</v>
       </c>
     </row>
   </sheetData>
@@ -994,7 +994,7 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>口径</t>
+          <t>统计范围</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
@@ -1026,17 +1026,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>真实薪资，主口径未缩尾</t>
+          <t>真实薪资，主统计范围未缩尾</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>35.996481</v>
+        <v>36.453256</v>
       </c>
       <c r="D2" t="n">
-        <v>66.29566699999999</v>
+        <v>67.24848</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5628300000000001</v>
+        <v>0.5501740000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34.899645</v>
+        <v>34.972903</v>
       </c>
       <c r="D3" t="n">
-        <v>68.221008</v>
+        <v>68.485865</v>
       </c>
       <c r="E3" t="n">
-        <v>0.537069</v>
+        <v>0.5334680000000001</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>目标口径 薪资下限</t>
+          <t>目标定义 薪资下限</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40.767003</v>
+        <v>40.857147</v>
       </c>
       <c r="D4" t="n">
-        <v>74.366242</v>
+        <v>74.279659</v>
       </c>
       <c r="E4" t="n">
-        <v>0.449913</v>
+        <v>0.451193</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>目标口径 薪资上限</t>
+          <t>目标定义 薪资上限</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47.690092</v>
+        <v>47.759384</v>
       </c>
       <c r="D5" t="n">
-        <v>74.066991</v>
+        <v>74.52978</v>
       </c>
       <c r="E5" t="n">
-        <v>0.454331</v>
+        <v>0.447491</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1138,7 +1138,7 @@
       <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.956402，共有特征 288 个</t>
+          <t>0.945440，共有特征 288 个</t>
         </is>
       </c>
     </row>
@@ -1158,7 +1158,7 @@
       <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.908353；0.882864（共同特征 288 个）</t>
+          <t>0.913358；0.868985（共同特征 288 个）</t>
         </is>
       </c>
     </row>
@@ -1210,16 +1210,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.880041</v>
+        <v>14.801961</v>
       </c>
       <c r="C2" t="n">
-        <v>0.094445</v>
+        <v>0.09357500000000001</v>
       </c>
       <c r="D2" t="n">
         <v>123</v>
       </c>
       <c r="E2" t="n">
-        <v>144.554975</v>
+        <v>143.869876</v>
       </c>
     </row>
     <row r="3">
@@ -1229,16 +1229,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>7.423312</v>
+        <v>6.95742</v>
       </c>
       <c r="C3" t="n">
-        <v>0.047117</v>
+        <v>0.043984</v>
       </c>
       <c r="D3" t="n">
         <v>882</v>
       </c>
       <c r="E3" t="n">
-        <v>7.34772</v>
+        <v>6.683126</v>
       </c>
     </row>
     <row r="4">
@@ -1248,16 +1248,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.956884</v>
+        <v>5.773383</v>
       </c>
       <c r="C4" t="n">
-        <v>0.037809</v>
+        <v>0.036498</v>
       </c>
       <c r="D4" t="n">
         <v>1091</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.19584</v>
+        <v>-5.159586</v>
       </c>
     </row>
     <row r="5">
@@ -1267,16 +1267,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.302168</v>
+        <v>5.433042</v>
       </c>
       <c r="C5" t="n">
-        <v>0.033653</v>
+        <v>0.034347</v>
       </c>
       <c r="D5" t="n">
         <v>2085</v>
       </c>
       <c r="E5" t="n">
-        <v>-1.096894</v>
+        <v>-0.856122</v>
       </c>
     </row>
     <row r="6">
@@ -1286,16 +1286,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>4.780053</v>
+        <v>5.027166</v>
       </c>
       <c r="C6" t="n">
-        <v>0.030339</v>
+        <v>0.031781</v>
       </c>
       <c r="D6" t="n">
         <v>1374</v>
       </c>
       <c r="E6" t="n">
-        <v>3.931998</v>
+        <v>4.113557</v>
       </c>
     </row>
     <row r="7">
@@ -1305,111 +1305,111 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.702895</v>
+        <v>4.773536</v>
       </c>
       <c r="C7" t="n">
-        <v>0.02985</v>
+        <v>0.030177</v>
       </c>
       <c r="D7" t="n">
         <v>1539</v>
       </c>
       <c r="E7" t="n">
-        <v>3.45854</v>
+        <v>3.544515</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>文本SVD4</t>
+          <t>岗位细分类集合=人工智能</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.091221</v>
+        <v>4.200456</v>
       </c>
       <c r="C8" t="n">
-        <v>0.025967</v>
+        <v>0.026555</v>
       </c>
       <c r="D8" t="n">
-        <v>970</v>
+        <v>200</v>
       </c>
       <c r="E8" t="n">
-        <v>4.719853</v>
+        <v>20.21463</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>学历等级</t>
+          <t>文本SVD4</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>3.754676</v>
+        <v>4.121337</v>
       </c>
       <c r="C9" t="n">
-        <v>0.023831</v>
+        <v>0.026054</v>
       </c>
       <c r="D9" t="n">
-        <v>1934</v>
+        <v>969</v>
       </c>
       <c r="E9" t="n">
-        <v>-0.810607</v>
+        <v>4.716519</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>文本SVD2</t>
+          <t>文本SVD5</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.719439</v>
+        <v>3.811497</v>
       </c>
       <c r="C10" t="n">
-        <v>0.023608</v>
+        <v>0.024096</v>
       </c>
       <c r="D10" t="n">
-        <v>985</v>
+        <v>1003</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.560242</v>
+        <v>-3.779334</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>岗位细分类集合=人工智能</t>
+          <t>文本SVD2</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.629611</v>
+        <v>3.776653</v>
       </c>
       <c r="C11" t="n">
-        <v>0.023038</v>
+        <v>0.023875</v>
       </c>
       <c r="D11" t="n">
-        <v>200</v>
+        <v>985</v>
       </c>
       <c r="E11" t="n">
-        <v>17.191847</v>
+        <v>-3.478788</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>文本SVD5</t>
+          <t>学历等级</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.595704</v>
+        <v>3.575971</v>
       </c>
       <c r="C12" t="n">
-        <v>0.022822</v>
+        <v>0.022607</v>
       </c>
       <c r="D12" t="n">
-        <v>1003</v>
+        <v>1934</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.540099</v>
+        <v>-0.6732050000000001</v>
       </c>
     </row>
     <row r="13">
@@ -1419,16 +1419,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.424103</v>
+        <v>3.34792</v>
       </c>
       <c r="C13" t="n">
-        <v>0.021733</v>
+        <v>0.021165</v>
       </c>
       <c r="D13" t="n">
-        <v>1083</v>
+        <v>1082</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.379037</v>
+        <v>-3.215762</v>
       </c>
     </row>
     <row r="14">
@@ -1438,16 +1438,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.085623</v>
+        <v>3.043902</v>
       </c>
       <c r="C14" t="n">
-        <v>0.019585</v>
+        <v>0.019243</v>
       </c>
       <c r="D14" t="n">
         <v>1111</v>
       </c>
       <c r="E14" t="n">
-        <v>3.068595</v>
+        <v>3.052286</v>
       </c>
     </row>
     <row r="15">
@@ -1457,16 +1457,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.685282</v>
+        <v>2.723848</v>
       </c>
       <c r="C15" t="n">
-        <v>0.017044</v>
+        <v>0.01722</v>
       </c>
       <c r="D15" t="n">
         <v>149</v>
       </c>
       <c r="E15" t="n">
-        <v>19.681614</v>
+        <v>20.37062</v>
       </c>
     </row>
     <row r="16">
@@ -1476,16 +1476,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.570484</v>
+        <v>2.393149</v>
       </c>
       <c r="C16" t="n">
-        <v>0.016315</v>
+        <v>0.015129</v>
       </c>
       <c r="D16" t="n">
         <v>2233</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.09597700000000001</v>
+        <v>-0.06637700000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1542,10 +1542,10 @@
         <v>74</v>
       </c>
       <c r="D2" t="n">
-        <v>21.380193</v>
+        <v>22.910199</v>
       </c>
       <c r="E2" t="n">
-        <v>1.725676</v>
+        <v>1.76088</v>
       </c>
     </row>
     <row r="3">
@@ -1561,10 +1561,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>45.147953</v>
+        <v>41.801341</v>
       </c>
       <c r="E3" t="n">
-        <v>0.608919</v>
+        <v>0.602917</v>
       </c>
     </row>
     <row r="4">
@@ -1580,10 +1580,10 @@
         <v>259</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.84764</v>
+        <v>-1.002237</v>
       </c>
       <c r="E4" t="n">
-        <v>0.523756</v>
+        <v>0.407285</v>
       </c>
     </row>
     <row r="5">
@@ -1599,29 +1599,29 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>4.736397</v>
+        <v>4.691634</v>
       </c>
       <c r="E5" t="n">
-        <v>0.365411</v>
+        <v>0.370409</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>数据分析</t>
+          <t>办公软件</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2718</v>
+        <v>2591</v>
       </c>
       <c r="C6" t="n">
-        <v>402</v>
+        <v>361</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.844594</v>
+        <v>-0.707606</v>
       </c>
       <c r="E6" t="n">
-        <v>0.361914</v>
+        <v>0.285662</v>
       </c>
     </row>
     <row r="7">
@@ -1637,295 +1637,295 @@
         <v>61</v>
       </c>
       <c r="D7" t="n">
-        <v>6.262866</v>
+        <v>4.814829</v>
       </c>
       <c r="E7" t="n">
-        <v>0.324723</v>
+        <v>0.274671</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>深度学习</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>572</v>
+        <v>619</v>
       </c>
       <c r="C8" t="n">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="D8" t="n">
-        <v>0.721616</v>
+        <v>-2.697057</v>
       </c>
       <c r="E8" t="n">
-        <v>0.210262</v>
+        <v>0.245455</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>项目管理</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>619</v>
+        <v>487</v>
       </c>
       <c r="C9" t="n">
-        <v>85</v>
+        <v>77</v>
       </c>
       <c r="D9" t="n">
-        <v>-2.270896</v>
+        <v>3.673901</v>
       </c>
       <c r="E9" t="n">
-        <v>0.205964</v>
+        <v>0.228526</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>项目管理</t>
+          <t>数据分析</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>487</v>
+        <v>2718</v>
       </c>
       <c r="C10" t="n">
-        <v>77</v>
+        <v>402</v>
       </c>
       <c r="D10" t="n">
-        <v>2.803566</v>
+        <v>-0.610657</v>
       </c>
       <c r="E10" t="n">
-        <v>0.171546</v>
+        <v>0.201132</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>深度学习</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>179</v>
+        <v>572</v>
       </c>
       <c r="C11" t="n">
-        <v>18</v>
+        <v>74</v>
       </c>
       <c r="D11" t="n">
-        <v>6.350753</v>
+        <v>-0.472882</v>
       </c>
       <c r="E11" t="n">
-        <v>0.12636</v>
+        <v>0.180905</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>295</v>
+        <v>179</v>
       </c>
       <c r="C12" t="n">
-        <v>40</v>
+        <v>18</v>
       </c>
       <c r="D12" t="n">
-        <v>3.436091</v>
+        <v>6.855472</v>
       </c>
       <c r="E12" t="n">
-        <v>0.123726</v>
+        <v>0.173304</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>多模态</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>446</v>
+        <v>231</v>
       </c>
       <c r="C13" t="n">
-        <v>65</v>
+        <v>27</v>
       </c>
       <c r="D13" t="n">
-        <v>1.649561</v>
+        <v>2.742308</v>
       </c>
       <c r="E13" t="n">
-        <v>0.105815</v>
+        <v>0.155267</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>231</v>
+        <v>295</v>
       </c>
       <c r="C14" t="n">
-        <v>27</v>
+        <v>40</v>
       </c>
       <c r="D14" t="n">
-        <v>0.549363</v>
+        <v>3.154364</v>
       </c>
       <c r="E14" t="n">
-        <v>0.09827</v>
+        <v>0.129567</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>大模型</t>
+          <t>Prompt Engineering</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>866</v>
+        <v>202</v>
       </c>
       <c r="C15" t="n">
-        <v>125</v>
+        <v>30</v>
       </c>
       <c r="D15" t="n">
-        <v>0.810434</v>
+        <v>-4.294281</v>
       </c>
       <c r="E15" t="n">
-        <v>0.09682399999999999</v>
+        <v>0.106327</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>办公软件</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2591</v>
+        <v>446</v>
       </c>
       <c r="C16" t="n">
-        <v>361</v>
+        <v>65</v>
       </c>
       <c r="D16" t="n">
-        <v>-0.190814</v>
+        <v>1.452553</v>
       </c>
       <c r="E16" t="n">
-        <v>0.081016</v>
+        <v>0.104653</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>大数据</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>238</v>
+        <v>301</v>
       </c>
       <c r="C17" t="n">
-        <v>35</v>
+        <v>49</v>
       </c>
       <c r="D17" t="n">
-        <v>3.029365</v>
+        <v>-2.430318</v>
       </c>
       <c r="E17" t="n">
-        <v>0.078837</v>
+        <v>0.10042</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>大数据</t>
+          <t>大模型</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>301</v>
+        <v>866</v>
       </c>
       <c r="C18" t="n">
-        <v>49</v>
+        <v>125</v>
       </c>
       <c r="D18" t="n">
-        <v>-1.788325</v>
+        <v>0.585608</v>
       </c>
       <c r="E18" t="n">
-        <v>0.069852</v>
+        <v>0.071897</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>MATLAB</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>205</v>
+        <v>118</v>
       </c>
       <c r="C19" t="n">
-        <v>29</v>
+        <v>15</v>
       </c>
       <c r="D19" t="n">
-        <v>2.809429</v>
+        <v>4.45055</v>
       </c>
       <c r="E19" t="n">
-        <v>0.06837600000000001</v>
+        <v>0.059554</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>人工智能</t>
+          <t>AIGC</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>2418</v>
+        <v>313</v>
       </c>
       <c r="C20" t="n">
-        <v>374</v>
+        <v>41</v>
       </c>
       <c r="D20" t="n">
-        <v>0.098874</v>
+        <v>-1.405586</v>
       </c>
       <c r="E20" t="n">
-        <v>0.056108</v>
+        <v>0.058098</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>产品设计</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>484</v>
+        <v>238</v>
       </c>
       <c r="C21" t="n">
-        <v>70</v>
+        <v>35</v>
       </c>
       <c r="D21" t="n">
-        <v>0.8492150000000001</v>
+        <v>1.850183</v>
       </c>
       <c r="E21" t="n">
-        <v>0.054547</v>
+        <v>0.056671</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>原型设计</t>
+          <t>产品设计</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>445</v>
+        <v>484</v>
       </c>
       <c r="C22" t="n">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D22" t="n">
-        <v>0.846513</v>
+        <v>0.762679</v>
       </c>
       <c r="E22" t="n">
-        <v>0.053749</v>
+        <v>0.054739</v>
       </c>
     </row>
     <row r="23">
@@ -1941,295 +1941,295 @@
         <v>37</v>
       </c>
       <c r="D23" t="n">
-        <v>1.5936</v>
+        <v>1.736432</v>
       </c>
       <c r="E23" t="n">
-        <v>0.048469</v>
+        <v>0.054161</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>TensorFlow</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>1387</v>
+        <v>277</v>
       </c>
       <c r="C24" t="n">
-        <v>208</v>
+        <v>36</v>
       </c>
       <c r="D24" t="n">
-        <v>0.188291</v>
+        <v>-1.733595</v>
       </c>
       <c r="E24" t="n">
-        <v>0.046979</v>
+        <v>0.052019</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>115</v>
+        <v>235</v>
       </c>
       <c r="C25" t="n">
-        <v>13</v>
+        <v>34</v>
       </c>
       <c r="D25" t="n">
-        <v>3.003416</v>
+        <v>1.579842</v>
       </c>
       <c r="E25" t="n">
-        <v>0.046541</v>
+        <v>0.051998</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>MATLAB</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>118</v>
+        <v>115</v>
       </c>
       <c r="C26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="D26" t="n">
-        <v>2.81403</v>
+        <v>3.122355</v>
       </c>
       <c r="E26" t="n">
-        <v>0.046058</v>
+        <v>0.050306</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>Prompt Engineering</t>
+          <t>人工智能</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>202</v>
+        <v>2418</v>
       </c>
       <c r="C27" t="n">
-        <v>30</v>
+        <v>374</v>
       </c>
       <c r="D27" t="n">
-        <v>-1.866092</v>
+        <v>-0.10739</v>
       </c>
       <c r="E27" t="n">
-        <v>0.045131</v>
+        <v>0.048397</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>数据科学</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>162</v>
+        <v>205</v>
       </c>
       <c r="C28" t="n">
-        <v>26</v>
+        <v>29</v>
       </c>
       <c r="D28" t="n">
-        <v>2.397954</v>
+        <v>2.041054</v>
       </c>
       <c r="E28" t="n">
-        <v>0.041583</v>
+        <v>0.045097</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>TensorFlow</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>277</v>
+        <v>1387</v>
       </c>
       <c r="C29" t="n">
-        <v>36</v>
+        <v>208</v>
       </c>
       <c r="D29" t="n">
-        <v>-1.154598</v>
+        <v>0.186899</v>
       </c>
       <c r="E29" t="n">
-        <v>0.040897</v>
+        <v>0.044681</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>235</v>
+        <v>162</v>
       </c>
       <c r="C30" t="n">
-        <v>34</v>
+        <v>26</v>
       </c>
       <c r="D30" t="n">
-        <v>1.212535</v>
+        <v>2.048257</v>
       </c>
       <c r="E30" t="n">
-        <v>0.039819</v>
+        <v>0.038385</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Vue</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>140</v>
+        <v>2737</v>
       </c>
       <c r="C31" t="n">
-        <v>22</v>
+        <v>426</v>
       </c>
       <c r="D31" t="n">
-        <v>-2.444467</v>
+        <v>-0.064752</v>
       </c>
       <c r="E31" t="n">
-        <v>0.038965</v>
+        <v>0.038338</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>数据挖掘</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>2737</v>
+        <v>156</v>
       </c>
       <c r="C32" t="n">
-        <v>426</v>
+        <v>24</v>
       </c>
       <c r="D32" t="n">
-        <v>-0.056578</v>
+        <v>2.003964</v>
       </c>
       <c r="E32" t="n">
-        <v>0.038748</v>
+        <v>0.035425</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>AIGC</t>
+          <t>原型设计</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>313</v>
+        <v>445</v>
       </c>
       <c r="C33" t="n">
-        <v>41</v>
+        <v>69</v>
       </c>
       <c r="D33" t="n">
-        <v>-0.523139</v>
+        <v>0.473324</v>
       </c>
       <c r="E33" t="n">
-        <v>0.033534</v>
+        <v>0.031416</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>微调</t>
+          <t>市场调研</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>132</v>
+        <v>437</v>
       </c>
       <c r="C34" t="n">
-        <v>16</v>
+        <v>57</v>
       </c>
       <c r="D34" t="n">
-        <v>1.641399</v>
+        <v>-0.4308</v>
       </c>
       <c r="E34" t="n">
-        <v>0.031374</v>
+        <v>0.023842</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>市场调研</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>437</v>
+        <v>210</v>
       </c>
       <c r="C35" t="n">
-        <v>57</v>
+        <v>36</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.522798</v>
+        <v>-0.741443</v>
       </c>
       <c r="E35" t="n">
-        <v>0.028559</v>
+        <v>0.023508</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>152</v>
+        <v>266</v>
       </c>
       <c r="C36" t="n">
-        <v>20</v>
+        <v>43</v>
       </c>
       <c r="D36" t="n">
-        <v>1.013909</v>
+        <v>0.241472</v>
       </c>
       <c r="E36" t="n">
-        <v>0.027348</v>
+        <v>0.019455</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>微调</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>266</v>
+        <v>132</v>
       </c>
       <c r="C37" t="n">
-        <v>43</v>
+        <v>16</v>
       </c>
       <c r="D37" t="n">
-        <v>0.604704</v>
+        <v>0.734278</v>
       </c>
       <c r="E37" t="n">
-        <v>0.022975</v>
+        <v>0.019239</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>Vue</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>599</v>
+        <v>140</v>
       </c>
       <c r="C38" t="n">
-        <v>84</v>
+        <v>22</v>
       </c>
       <c r="D38" t="n">
-        <v>0.248595</v>
+        <v>-1.016467</v>
       </c>
       <c r="E38" t="n">
-        <v>0.021342</v>
+        <v>0.018456</v>
       </c>
     </row>
     <row r="39">
@@ -2245,48 +2245,48 @@
         <v>52</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.148701</v>
+        <v>-0.057313</v>
       </c>
       <c r="E39" t="n">
-        <v>0.021112</v>
+        <v>0.015495</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>单元测试</t>
+          <t>内容运营</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>123</v>
+        <v>774</v>
       </c>
       <c r="C40" t="n">
-        <v>19</v>
+        <v>111</v>
       </c>
       <c r="D40" t="n">
-        <v>-1.289597</v>
+        <v>0.149377</v>
       </c>
       <c r="E40" t="n">
-        <v>0.018956</v>
+        <v>0.013209</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>数据挖掘</t>
+          <t>用户研究</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>156</v>
+        <v>383</v>
       </c>
       <c r="C41" t="n">
-        <v>24</v>
+        <v>61</v>
       </c>
       <c r="D41" t="n">
-        <v>0.121996</v>
+        <v>0.21443</v>
       </c>
       <c r="E41" t="n">
-        <v>0.017981</v>
+        <v>0.012858</v>
       </c>
     </row>
     <row r="42">
@@ -2302,86 +2302,86 @@
         <v>200</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.040771</v>
+        <v>-0.019068</v>
       </c>
       <c r="E42" t="n">
-        <v>0.017453</v>
+        <v>0.01086</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>210</v>
+        <v>599</v>
       </c>
       <c r="C43" t="n">
-        <v>36</v>
+        <v>84</v>
       </c>
       <c r="D43" t="n">
-        <v>-0.689343</v>
+        <v>0.133505</v>
       </c>
       <c r="E43" t="n">
-        <v>0.016438</v>
+        <v>0.009528999999999999</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>用户研究</t>
+          <t>数据可视化</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>383</v>
+        <v>409</v>
       </c>
       <c r="C44" t="n">
-        <v>61</v>
+        <v>67</v>
       </c>
       <c r="D44" t="n">
-        <v>0.259956</v>
+        <v>0.12837</v>
       </c>
       <c r="E44" t="n">
-        <v>0.015116</v>
+        <v>0.007997000000000001</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>内容运营</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>774</v>
+        <v>110</v>
       </c>
       <c r="C45" t="n">
-        <v>111</v>
+        <v>10</v>
       </c>
       <c r="D45" t="n">
-        <v>0.134654</v>
+        <v>0.594403</v>
       </c>
       <c r="E45" t="n">
-        <v>0.012448</v>
+        <v>0.007592</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>数据可视化</t>
+          <t>React</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>409</v>
+        <v>126</v>
       </c>
       <c r="C46" t="n">
-        <v>67</v>
+        <v>23</v>
       </c>
       <c r="D46" t="n">
-        <v>0.173359</v>
+        <v>-0.384752</v>
       </c>
       <c r="E46" t="n">
-        <v>0.011326</v>
+        <v>0.005533</v>
       </c>
     </row>
     <row r="47">
@@ -2397,80 +2397,80 @@
         <v>43</v>
       </c>
       <c r="D47" t="n">
-        <v>0.185257</v>
+        <v>0.037827</v>
       </c>
       <c r="E47" t="n">
-        <v>0.008045</v>
+        <v>0.001675</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>110</v>
+        <v>143</v>
       </c>
       <c r="C48" t="n">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="D48" t="n">
-        <v>-0.638734</v>
+        <v>0</v>
       </c>
       <c r="E48" t="n">
-        <v>0.007741</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>165</v>
+        <v>152</v>
       </c>
       <c r="C49" t="n">
-        <v>25</v>
+        <v>20</v>
       </c>
       <c r="D49" t="n">
-        <v>0.165787</v>
+        <v>0</v>
       </c>
       <c r="E49" t="n">
-        <v>0.003893</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>126</v>
+        <v>165</v>
       </c>
       <c r="C50" t="n">
-        <v>23</v>
+        <v>25</v>
       </c>
       <c r="D50" t="n">
-        <v>-0.225473</v>
+        <v>0</v>
       </c>
       <c r="E50" t="n">
-        <v>0.003183</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>单元测试</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>143</v>
+        <v>123</v>
       </c>
       <c r="C51" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2525,7 +2525,7 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>重算（严格口径周期层，n = 17131）</t>
+          <t>重算（严格统计范围周期层，n = 17131）</t>
         </is>
       </c>
     </row>
@@ -2788,22 +2788,22 @@
         <v>232</v>
       </c>
       <c r="C4" t="n">
-        <v>36.51492</v>
+        <v>36.190873</v>
       </c>
       <c r="D4" t="n">
-        <v>71.21809500000001</v>
+        <v>69.87125899999999</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5737</v>
+        <v>0.5896709999999999</v>
       </c>
       <c r="F4" t="n">
-        <v>36.224869</v>
+        <v>35.968386</v>
       </c>
       <c r="G4" t="n">
-        <v>66.197988</v>
+        <v>65.953063</v>
       </c>
       <c r="H4" t="n">
-        <v>0.564117</v>
+        <v>0.567337</v>
       </c>
       <c r="I4" t="n">
         <v>10418</v>
@@ -2825,22 +2825,22 @@
         <v>288</v>
       </c>
       <c r="C5" t="n">
-        <v>36.038993</v>
+        <v>36.635124</v>
       </c>
       <c r="D5" t="n">
-        <v>69.9654</v>
+        <v>70.771012</v>
       </c>
       <c r="E5" t="n">
-        <v>0.588565</v>
+        <v>0.579035</v>
       </c>
       <c r="F5" t="n">
-        <v>35.996481</v>
+        <v>36.453256</v>
       </c>
       <c r="G5" t="n">
-        <v>66.29566699999999</v>
+        <v>67.24848</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5628300000000001</v>
+        <v>0.5501740000000001</v>
       </c>
       <c r="I5" t="n">
         <v>10418</v>
@@ -2862,22 +2862,22 @@
         <v>290</v>
       </c>
       <c r="C6" t="n">
-        <v>36.126096</v>
+        <v>36.258904</v>
       </c>
       <c r="D6" t="n">
-        <v>69.77090800000001</v>
+        <v>69.909462</v>
       </c>
       <c r="E6" t="n">
-        <v>0.590849</v>
+        <v>0.589222</v>
       </c>
       <c r="F6" t="n">
-        <v>36.396036</v>
+        <v>36.417074</v>
       </c>
       <c r="G6" t="n">
-        <v>66.949583</v>
+        <v>67.001621</v>
       </c>
       <c r="H6" t="n">
-        <v>0.554163</v>
+        <v>0.55347</v>
       </c>
       <c r="I6" t="n">
         <v>10418</v>
@@ -2972,19 +2972,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36.038993</v>
+        <v>36.635124</v>
       </c>
       <c r="E2" t="n">
-        <v>36.126096</v>
+        <v>36.258904</v>
       </c>
       <c r="F2" t="n">
-        <v>-0.087103</v>
+        <v>0.37622</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.557664</v>
+        <v>-0.053566</v>
       </c>
       <c r="H2" t="n">
-        <v>0.407551</v>
+        <v>0.793957</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3012,19 +3012,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>35.996481</v>
+        <v>36.453256</v>
       </c>
       <c r="E3" t="n">
-        <v>36.396036</v>
+        <v>36.417074</v>
       </c>
       <c r="F3" t="n">
-        <v>-0.399554</v>
+        <v>0.036182</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.863312</v>
+        <v>-0.419526</v>
       </c>
       <c r="H3" t="n">
-        <v>0.056279</v>
+        <v>0.471827</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3135,16 +3135,16 @@
         <v>36.449958</v>
       </c>
       <c r="E6" t="n">
-        <v>36.51492</v>
+        <v>36.190873</v>
       </c>
       <c r="F6" t="n">
-        <v>-0.06496200000000001</v>
+        <v>0.259085</v>
       </c>
       <c r="G6" t="n">
-        <v>-1.149532</v>
+        <v>-0.806226</v>
       </c>
       <c r="H6" t="n">
-        <v>1.124648</v>
+        <v>1.398121</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3175,16 +3175,16 @@
         <v>34.712727</v>
       </c>
       <c r="E7" t="n">
-        <v>36.224869</v>
+        <v>35.968386</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.512142</v>
+        <v>-1.255659</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.542551</v>
+        <v>-2.266797</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.490906</v>
+        <v>-0.187017</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3215,16 +3215,16 @@
         <v>36.449958</v>
       </c>
       <c r="E8" t="n">
-        <v>36.038993</v>
+        <v>36.635124</v>
       </c>
       <c r="F8" t="n">
-        <v>0.410965</v>
+        <v>-0.185166</v>
       </c>
       <c r="G8" t="n">
-        <v>-0.709811</v>
+        <v>-1.298019</v>
       </c>
       <c r="H8" t="n">
-        <v>1.659958</v>
+        <v>0.980715</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -3255,16 +3255,16 @@
         <v>34.712727</v>
       </c>
       <c r="E9" t="n">
-        <v>35.996481</v>
+        <v>36.453256</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.283754</v>
+        <v>-1.740529</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.397711</v>
+        <v>-2.838029</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.275467</v>
+        <v>-0.6043500000000001</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -3343,22 +3343,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.038993</v>
+        <v>36.635124</v>
       </c>
       <c r="D2" t="n">
-        <v>69.9654</v>
+        <v>70.771012</v>
       </c>
       <c r="E2" t="n">
-        <v>0.588565</v>
+        <v>0.579035</v>
       </c>
       <c r="F2" t="n">
-        <v>35.996481</v>
+        <v>36.453256</v>
       </c>
       <c r="G2" t="n">
-        <v>66.29566699999999</v>
+        <v>67.24848</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5628300000000001</v>
+        <v>0.5501740000000001</v>
       </c>
     </row>
     <row r="3">
@@ -3373,22 +3373,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.872254</v>
+        <v>36.709331</v>
       </c>
       <c r="D3" t="n">
-        <v>68.684195</v>
+        <v>69.01518299999999</v>
       </c>
       <c r="E3" t="n">
-        <v>0.603495</v>
+        <v>0.599664</v>
       </c>
       <c r="F3" t="n">
-        <v>36.610101</v>
+        <v>36.374433</v>
       </c>
       <c r="G3" t="n">
-        <v>65.638513</v>
+        <v>65.219776</v>
       </c>
       <c r="H3" t="n">
-        <v>0.571454</v>
+        <v>0.576904</v>
       </c>
     </row>
     <row r="4">
@@ -3403,22 +3403,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38.146395</v>
+        <v>38.232707</v>
       </c>
       <c r="D4" t="n">
-        <v>73.747653</v>
+        <v>74.244028</v>
       </c>
       <c r="E4" t="n">
-        <v>0.542879</v>
+        <v>0.536705</v>
       </c>
       <c r="F4" t="n">
-        <v>37.069057</v>
+        <v>37.050243</v>
       </c>
       <c r="G4" t="n">
-        <v>69.085273</v>
+        <v>68.836217</v>
       </c>
       <c r="H4" t="n">
-        <v>0.525265</v>
+        <v>0.528682</v>
       </c>
     </row>
     <row r="5">
@@ -3433,22 +3433,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.30729</v>
+        <v>45.307314</v>
       </c>
       <c r="D5" t="n">
-        <v>85.69307000000001</v>
+        <v>85.69301400000001</v>
       </c>
       <c r="E5" t="n">
         <v>0.3828</v>
       </c>
       <c r="F5" t="n">
-        <v>43.739258</v>
+        <v>43.739362</v>
       </c>
       <c r="G5" t="n">
-        <v>77.43084500000001</v>
+        <v>77.430978</v>
       </c>
       <c r="H5" t="n">
-        <v>0.403641</v>
+        <v>0.403639</v>
       </c>
     </row>
     <row r="6">
@@ -3564,13 +3564,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>35.996481</v>
+        <v>36.453256</v>
       </c>
       <c r="C2" t="n">
-        <v>66.29566699999999</v>
+        <v>67.24848</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5628300000000001</v>
+        <v>0.5501740000000001</v>
       </c>
       <c r="E2" t="n">
         <v>2233</v>
@@ -3586,13 +3586,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.476021</v>
+        <v>35.301511</v>
       </c>
       <c r="C3" t="n">
-        <v>64.80933400000001</v>
+        <v>64.440247</v>
       </c>
       <c r="D3" t="n">
-        <v>0.582213</v>
+        <v>0.586958</v>
       </c>
       <c r="E3" t="n">
         <v>2233</v>
@@ -3657,10 +3657,10 @@
         <v>2233</v>
       </c>
       <c r="D2" t="n">
-        <v>35.476021</v>
+        <v>35.301511</v>
       </c>
       <c r="E2" t="n">
-        <v>64.80933400000001</v>
+        <v>64.440247</v>
       </c>
     </row>
     <row r="3">
@@ -3678,10 +3678,10 @@
         <v>628</v>
       </c>
       <c r="D3" t="n">
-        <v>35.433615</v>
+        <v>36.016921</v>
       </c>
       <c r="E3" t="n">
-        <v>49.039927</v>
+        <v>49.966743</v>
       </c>
     </row>
     <row r="4">
@@ -3699,10 +3699,10 @@
         <v>702</v>
       </c>
       <c r="D4" t="n">
-        <v>22.718336</v>
+        <v>22.401059</v>
       </c>
       <c r="E4" t="n">
-        <v>31.864841</v>
+        <v>31.18655</v>
       </c>
     </row>
     <row r="5">
@@ -3720,10 +3720,10 @@
         <v>477</v>
       </c>
       <c r="D5" t="n">
-        <v>29.407602</v>
+        <v>28.670529</v>
       </c>
       <c r="E5" t="n">
-        <v>40.13135</v>
+        <v>39.105057</v>
       </c>
     </row>
     <row r="6">
@@ -3741,10 +3741,10 @@
         <v>426</v>
       </c>
       <c r="D6" t="n">
-        <v>63.356684</v>
+        <v>62.930189</v>
       </c>
       <c r="E6" t="n">
-        <v>122.454002</v>
+        <v>121.536766</v>
       </c>
     </row>
   </sheetData>
@@ -3793,10 +3793,10 @@
         <v>933</v>
       </c>
       <c r="C2" t="n">
-        <v>29.779193</v>
+        <v>29.210548</v>
       </c>
       <c r="D2" t="n">
-        <v>44.008937</v>
+        <v>43.586832</v>
       </c>
     </row>
     <row r="3">
@@ -3809,42 +3809,42 @@
         <v>1493</v>
       </c>
       <c r="C3" t="n">
-        <v>29.817912</v>
+        <v>29.464841</v>
       </c>
       <c r="D3" t="n">
-        <v>43.766176</v>
+        <v>43.325227</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>游戏</t>
+          <t>技术管理</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="C4" t="n">
-        <v>32.2488</v>
+        <v>32.382271</v>
       </c>
       <c r="D4" t="n">
-        <v>41.036596</v>
+        <v>44.49019</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>技术管理</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C5" t="n">
-        <v>32.524719</v>
+        <v>33.572045</v>
       </c>
       <c r="D5" t="n">
-        <v>44.458097</v>
+        <v>43.358692</v>
       </c>
     </row>
     <row r="6">
@@ -3857,10 +3857,10 @@
         <v>164</v>
       </c>
       <c r="C6" t="n">
-        <v>32.828397</v>
+        <v>34.689506</v>
       </c>
       <c r="D6" t="n">
-        <v>58.0466</v>
+        <v>60.017712</v>
       </c>
     </row>
     <row r="7">
@@ -3873,10 +3873,10 @@
         <v>437</v>
       </c>
       <c r="C7" t="n">
-        <v>49.8513</v>
+        <v>49.573358</v>
       </c>
       <c r="D7" t="n">
-        <v>105.343391</v>
+        <v>105.35052</v>
       </c>
     </row>
     <row r="8">
@@ -3889,10 +3889,10 @@
         <v>499</v>
       </c>
       <c r="C8" t="n">
-        <v>55.287805</v>
+        <v>55.645736</v>
       </c>
       <c r="D8" t="n">
-        <v>109.878365</v>
+        <v>109.651422</v>
       </c>
     </row>
     <row r="9">
@@ -3905,10 +3905,10 @@
         <v>205</v>
       </c>
       <c r="C9" t="n">
-        <v>56.106477</v>
+        <v>56.91957</v>
       </c>
       <c r="D9" t="n">
-        <v>113.902471</v>
+        <v>115.128414</v>
       </c>
     </row>
     <row r="10">
@@ -3921,10 +3921,10 @@
         <v>141</v>
       </c>
       <c r="C10" t="n">
-        <v>56.218217</v>
+        <v>57.127111</v>
       </c>
       <c r="D10" t="n">
-        <v>107.573772</v>
+        <v>108.600865</v>
       </c>
     </row>
     <row r="11">
@@ -3937,10 +3937,10 @@
         <v>363</v>
       </c>
       <c r="C11" t="n">
-        <v>57.085812</v>
+        <v>57.361217</v>
       </c>
       <c r="D11" t="n">
-        <v>111.557305</v>
+        <v>110.842032</v>
       </c>
     </row>
     <row r="12">
@@ -3953,10 +3953,10 @@
         <v>250</v>
       </c>
       <c r="C12" t="n">
-        <v>57.328417</v>
+        <v>57.864117</v>
       </c>
       <c r="D12" t="n">
-        <v>130.943976</v>
+        <v>130.106045</v>
       </c>
     </row>
     <row r="13">
@@ -3969,10 +3969,10 @@
         <v>237</v>
       </c>
       <c r="C13" t="n">
-        <v>60.212018</v>
+        <v>60.536126</v>
       </c>
       <c r="D13" t="n">
-        <v>133.553675</v>
+        <v>132.473527</v>
       </c>
     </row>
   </sheetData>
@@ -4031,16 +4031,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.038993</v>
+        <v>36.635124</v>
       </c>
       <c r="D2" t="n">
-        <v>35.996481</v>
+        <v>36.453256</v>
       </c>
       <c r="E2" t="n">
-        <v>66.29566699999999</v>
+        <v>67.24848</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5628300000000001</v>
+        <v>0.5501740000000001</v>
       </c>
     </row>
     <row r="3">
@@ -4053,16 +4053,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.872254</v>
+        <v>36.709331</v>
       </c>
       <c r="D3" t="n">
-        <v>36.610101</v>
+        <v>36.374433</v>
       </c>
       <c r="E3" t="n">
-        <v>65.638513</v>
+        <v>65.219776</v>
       </c>
       <c r="F3" t="n">
-        <v>0.571454</v>
+        <v>0.576904</v>
       </c>
     </row>
     <row r="4">
@@ -4075,16 +4075,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34.7275</v>
+        <v>35.052459</v>
       </c>
       <c r="D4" t="n">
-        <v>35.330233</v>
+        <v>35.07521</v>
       </c>
       <c r="E4" t="n">
-        <v>63.195894</v>
+        <v>63.225293</v>
       </c>
       <c r="F4" t="n">
-        <v>0.58843</v>
+        <v>0.588047</v>
       </c>
     </row>
     <row r="5">
@@ -4097,16 +4097,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>35.968016</v>
+        <v>36.079428</v>
       </c>
       <c r="D5" t="n">
-        <v>36.632071</v>
+        <v>36.49674</v>
       </c>
       <c r="E5" t="n">
-        <v>64.588768</v>
+        <v>64.19069399999999</v>
       </c>
       <c r="F5" t="n">
-        <v>0.570087</v>
+        <v>0.57537</v>
       </c>
     </row>
     <row r="6">
@@ -4119,16 +4119,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.21049</v>
+        <v>34.287021</v>
       </c>
       <c r="D6" t="n">
-        <v>35.884176</v>
+        <v>35.423573</v>
       </c>
       <c r="E6" t="n">
-        <v>64.677241</v>
+        <v>64.722156</v>
       </c>
       <c r="F6" t="n">
-        <v>0.578532</v>
+        <v>0.577947</v>
       </c>
     </row>
     <row r="7">
@@ -4141,16 +4141,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35.505143</v>
+        <v>35.182884</v>
       </c>
       <c r="D7" t="n">
-        <v>36.179734</v>
+        <v>36.026658</v>
       </c>
       <c r="E7" t="n">
-        <v>63.504338</v>
+        <v>63.529348</v>
       </c>
       <c r="F7" t="n">
-        <v>0.59368</v>
+        <v>0.59336</v>
       </c>
     </row>
     <row r="8">
@@ -4163,16 +4163,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>35.549074</v>
+        <v>35.407767</v>
       </c>
       <c r="D8" t="n">
-        <v>35.101361</v>
+        <v>34.688367</v>
       </c>
       <c r="E8" t="n">
-        <v>59.80829</v>
+        <v>59.132984</v>
       </c>
       <c r="F8" t="n">
-        <v>0.684782</v>
+        <v>0.69186</v>
       </c>
     </row>
     <row r="9">
@@ -4185,16 +4185,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>35.993351</v>
+        <v>36.189409</v>
       </c>
       <c r="D9" t="n">
-        <v>35.684738</v>
+        <v>35.762937</v>
       </c>
       <c r="E9" t="n">
-        <v>59.764083</v>
+        <v>60.205093</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6852470000000001</v>
+        <v>0.680585</v>
       </c>
     </row>
     <row r="10">
@@ -4207,16 +4207,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37.198006</v>
+        <v>37.379754</v>
       </c>
       <c r="D10" t="n">
-        <v>36.313587</v>
+        <v>36.375737</v>
       </c>
       <c r="E10" t="n">
-        <v>67.662936</v>
+        <v>68.037413</v>
       </c>
       <c r="F10" t="n">
-        <v>0.557048</v>
+        <v>0.552131</v>
       </c>
     </row>
     <row r="11">
@@ -4229,16 +4229,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.494746</v>
+        <v>38.486587</v>
       </c>
       <c r="D11" t="n">
-        <v>36.696483</v>
+        <v>36.442314</v>
       </c>
       <c r="E11" t="n">
-        <v>68.182388</v>
+        <v>66.422023</v>
       </c>
       <c r="F11" t="n">
-        <v>0.550221</v>
+        <v>0.573146</v>
       </c>
     </row>
   </sheetData>
@@ -4289,16 +4289,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.566702</v>
+        <v>36.529528</v>
       </c>
       <c r="C2" t="n">
-        <v>1.185831</v>
+        <v>1.224146</v>
       </c>
       <c r="D2" t="n">
-        <v>36.360625</v>
+        <v>36.220616</v>
       </c>
       <c r="E2" t="n">
-        <v>0.429612</v>
+        <v>0.3147</v>
       </c>
     </row>
     <row r="3">
@@ -4308,16 +4308,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.544813</v>
+        <v>35.752425</v>
       </c>
       <c r="C3" t="n">
-        <v>1.164656</v>
+        <v>1.243333</v>
       </c>
       <c r="D3" t="n">
-        <v>35.725168</v>
+        <v>35.603229</v>
       </c>
       <c r="E3" t="n">
-        <v>0.497554</v>
+        <v>0.785393</v>
       </c>
     </row>
   </sheetData>

--- a/course-design-2/outputs/tables/ch7/52_stage26_4_metrics_final.xlsx
+++ b/course-design-2/outputs/tables/ch7/52_stage26_4_metrics_final.xlsx
@@ -1,27 +1,27 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="01_三种划分统一协议" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="02_消融五配置" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="03_消融增量bootstrap" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="04_模型比较" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="05_最终模型测试集" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="06_分组预测误差四分位" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="07_岗位大类预测误差" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="08_多种子明细" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="09_多种子汇总" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="10_公司分组多次划分" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="11_公司分组汇总" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="12_稳健性对照" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="13_主模型SHAP特征" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="14_技能SHAP" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="15_图4-4新旧数据对照" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="01_三种划分统一协议" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="02_消融五配置" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="03_消融增量bootstrap" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="04_模型比较" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="05_最终模型测试集" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="06_分组预测误差四分位" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="07_岗位大类预测误差" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="08_多种子明细" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="09_多种子汇总" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="10_公司分组多次划分" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="11_公司分组汇总" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="12_稳健性对照" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="13_主模型SHAP特征" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="14_技能SHAP" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="15_图4-4新旧数据对照" sheetId="15" state="visible" r:id="rId15"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -546,31 +546,31 @@
         <v>44</v>
       </c>
       <c r="G2" t="n">
-        <v>36.453256</v>
+        <v>35.996481</v>
       </c>
       <c r="H2" t="n">
-        <v>67.24848</v>
+        <v>66.29566699999999</v>
       </c>
       <c r="I2" t="n">
-        <v>0.5501740000000001</v>
+        <v>0.5628300000000001</v>
       </c>
       <c r="J2" t="n">
-        <v>36.635124</v>
+        <v>36.038993</v>
       </c>
       <c r="K2" t="n">
-        <v>70.771012</v>
+        <v>69.9654</v>
       </c>
       <c r="L2" t="n">
-        <v>0.579035</v>
+        <v>0.588565</v>
       </c>
       <c r="M2" t="n">
-        <v>36.354494</v>
+        <v>36.451863</v>
       </c>
       <c r="N2" t="n">
-        <v>67.36623</v>
+        <v>66.85369900000001</v>
       </c>
       <c r="O2" t="n">
-        <v>0.548597</v>
+        <v>0.55544</v>
       </c>
       <c r="P2" t="n">
         <v>308</v>
@@ -598,31 +598,31 @@
         <v>43</v>
       </c>
       <c r="G3" t="n">
-        <v>52.794804</v>
+        <v>51.983919</v>
       </c>
       <c r="H3" t="n">
-        <v>104.800307</v>
+        <v>103.57182</v>
       </c>
       <c r="I3" t="n">
-        <v>0.115272</v>
+        <v>0.135892</v>
       </c>
       <c r="J3" t="n">
-        <v>56.773993</v>
+        <v>56.723294</v>
       </c>
       <c r="K3" t="n">
-        <v>99.90326399999999</v>
+        <v>100.257122</v>
       </c>
       <c r="L3" t="n">
-        <v>0.143159</v>
+        <v>0.137079</v>
       </c>
       <c r="M3" t="n">
-        <v>51.629921</v>
+        <v>52.093534</v>
       </c>
       <c r="N3" t="n">
-        <v>103.613495</v>
+        <v>103.691486</v>
       </c>
       <c r="O3" t="n">
-        <v>0.135197</v>
+        <v>0.133895</v>
       </c>
       <c r="P3" t="n">
         <v>299</v>
@@ -650,31 +650,31 @@
         <v>45</v>
       </c>
       <c r="G4" t="n">
-        <v>31.818072</v>
+        <v>31.719235</v>
       </c>
       <c r="H4" t="n">
-        <v>47.694496</v>
+        <v>47.615814</v>
       </c>
       <c r="I4" t="n">
-        <v>0.655173</v>
+        <v>0.6563099999999999</v>
       </c>
       <c r="J4" t="n">
-        <v>39.323111</v>
+        <v>38.853433</v>
       </c>
       <c r="K4" t="n">
-        <v>72.798478</v>
+        <v>72.325975</v>
       </c>
       <c r="L4" t="n">
-        <v>0.502343</v>
+        <v>0.508782</v>
       </c>
       <c r="M4" t="n">
-        <v>31.858455</v>
+        <v>32.132572</v>
       </c>
       <c r="N4" t="n">
-        <v>48.03658</v>
+        <v>47.817303</v>
       </c>
       <c r="O4" t="n">
-        <v>0.650209</v>
+        <v>0.6533949999999999</v>
       </c>
       <c r="P4" t="n">
         <v>309</v>
@@ -753,13 +753,13 @@
         <v>1688</v>
       </c>
       <c r="F2" t="n">
-        <v>52.794804</v>
+        <v>51.983919</v>
       </c>
       <c r="G2" t="n">
-        <v>104.800307</v>
+        <v>103.57182</v>
       </c>
       <c r="H2" t="n">
-        <v>0.115272</v>
+        <v>0.135892</v>
       </c>
     </row>
     <row r="3">
@@ -779,13 +779,13 @@
         <v>2842</v>
       </c>
       <c r="F3" t="n">
-        <v>80.844548</v>
+        <v>81.46315</v>
       </c>
       <c r="G3" t="n">
-        <v>120.154008</v>
+        <v>121.563886</v>
       </c>
       <c r="H3" t="n">
-        <v>0.040708</v>
+        <v>0.018063</v>
       </c>
     </row>
     <row r="4">
@@ -805,13 +805,13 @@
         <v>1988</v>
       </c>
       <c r="F4" t="n">
-        <v>38.738047</v>
+        <v>38.831912</v>
       </c>
       <c r="G4" t="n">
-        <v>61.774548</v>
+        <v>62.099138</v>
       </c>
       <c r="H4" t="n">
-        <v>0.155521</v>
+        <v>0.146623</v>
       </c>
     </row>
     <row r="5">
@@ -831,13 +831,13 @@
         <v>1867</v>
       </c>
       <c r="F5" t="n">
-        <v>48.936058</v>
+        <v>49.441596</v>
       </c>
       <c r="G5" t="n">
-        <v>101.608421</v>
+        <v>101.740059</v>
       </c>
       <c r="H5" t="n">
-        <v>0.118743</v>
+        <v>0.116458</v>
       </c>
     </row>
     <row r="6">
@@ -857,13 +857,13 @@
         <v>1870</v>
       </c>
       <c r="F6" t="n">
-        <v>45.683421</v>
+        <v>45.73755</v>
       </c>
       <c r="G6" t="n">
-        <v>79.04685600000001</v>
+        <v>79.59930300000001</v>
       </c>
       <c r="H6" t="n">
-        <v>0.102307</v>
+        <v>0.089715</v>
       </c>
     </row>
   </sheetData>
@@ -899,7 +899,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>53.399376</v>
+        <v>53.491625</v>
       </c>
     </row>
     <row r="3">
@@ -909,7 +909,7 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>16.186528</v>
+        <v>16.402096</v>
       </c>
     </row>
     <row r="4">
@@ -919,7 +919,7 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>38.738047</v>
+        <v>38.831912</v>
       </c>
     </row>
     <row r="5">
@@ -929,7 +929,7 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>80.844548</v>
+        <v>81.46315</v>
       </c>
     </row>
     <row r="6">
@@ -939,7 +939,7 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>93.476828</v>
+        <v>93.71484100000001</v>
       </c>
     </row>
     <row r="7">
@@ -949,7 +949,7 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>23.01779</v>
+        <v>23.108086</v>
       </c>
     </row>
     <row r="8">
@@ -959,7 +959,7 @@
         </is>
       </c>
       <c r="B8" t="n">
-        <v>0.10651</v>
+        <v>0.10135</v>
       </c>
     </row>
     <row r="9">
@@ -969,7 +969,7 @@
         </is>
       </c>
       <c r="B9" t="n">
-        <v>0.041761</v>
+        <v>0.05134</v>
       </c>
     </row>
   </sheetData>
@@ -1026,17 +1026,17 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>真实薪资，主统计范围未缩尾</t>
+          <t>真实薪资，主口径未缩尾</t>
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.453256</v>
+        <v>35.996481</v>
       </c>
       <c r="D2" t="n">
-        <v>67.24848</v>
+        <v>66.29566699999999</v>
       </c>
       <c r="E2" t="n">
-        <v>0.5501740000000001</v>
+        <v>0.5628300000000001</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -1056,13 +1056,13 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>34.972903</v>
+        <v>34.899645</v>
       </c>
       <c r="D3" t="n">
-        <v>68.485865</v>
+        <v>68.221008</v>
       </c>
       <c r="E3" t="n">
-        <v>0.5334680000000001</v>
+        <v>0.537069</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
@@ -1073,7 +1073,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>目标定义 薪资下限</t>
+          <t>目标口径 薪资下限</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1082,13 +1082,13 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>40.857147</v>
+        <v>40.767003</v>
       </c>
       <c r="D4" t="n">
-        <v>74.279659</v>
+        <v>74.366242</v>
       </c>
       <c r="E4" t="n">
-        <v>0.451193</v>
+        <v>0.449913</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
@@ -1099,7 +1099,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>目标定义 薪资上限</t>
+          <t>目标口径 薪资上限</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -1108,13 +1108,13 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>47.759384</v>
+        <v>47.690092</v>
       </c>
       <c r="D5" t="n">
-        <v>74.52978</v>
+        <v>74.066991</v>
       </c>
       <c r="E5" t="n">
-        <v>0.447491</v>
+        <v>0.454331</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
@@ -1133,12 +1133,9 @@
           <t>winsorize 与主模型 gain 排名的 Spearman</t>
         </is>
       </c>
-      <c r="C6" t="inlineStr"/>
-      <c r="D6" t="inlineStr"/>
-      <c r="E6" t="inlineStr"/>
       <c r="F6" t="inlineStr">
         <is>
-          <t>0.945440，共有特征 288 个</t>
+          <t>0.956402，共有特征 288 个</t>
         </is>
       </c>
     </row>
@@ -1153,12 +1150,9 @@
           <t>三种随机种子 42、7、2024 与主模型平均绝对SHAP值排名的 Spearman</t>
         </is>
       </c>
-      <c r="C7" t="inlineStr"/>
-      <c r="D7" t="inlineStr"/>
-      <c r="E7" t="inlineStr"/>
       <c r="F7" t="inlineStr">
         <is>
-          <t>0.913358；0.868985（共同特征 288 个）</t>
+          <t>0.908353；0.882864（共同特征 288 个）</t>
         </is>
       </c>
     </row>
@@ -1210,16 +1204,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>14.801961</v>
+        <v>14.880041</v>
       </c>
       <c r="C2" t="n">
-        <v>0.09357500000000001</v>
+        <v>0.094445</v>
       </c>
       <c r="D2" t="n">
         <v>123</v>
       </c>
       <c r="E2" t="n">
-        <v>143.869876</v>
+        <v>144.554975</v>
       </c>
     </row>
     <row r="3">
@@ -1229,16 +1223,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>6.95742</v>
+        <v>7.423312</v>
       </c>
       <c r="C3" t="n">
-        <v>0.043984</v>
+        <v>0.047117</v>
       </c>
       <c r="D3" t="n">
         <v>882</v>
       </c>
       <c r="E3" t="n">
-        <v>6.683126</v>
+        <v>7.34772</v>
       </c>
     </row>
     <row r="4">
@@ -1248,16 +1242,16 @@
         </is>
       </c>
       <c r="B4" t="n">
-        <v>5.773383</v>
+        <v>5.956884</v>
       </c>
       <c r="C4" t="n">
-        <v>0.036498</v>
+        <v>0.037809</v>
       </c>
       <c r="D4" t="n">
         <v>1091</v>
       </c>
       <c r="E4" t="n">
-        <v>-5.159586</v>
+        <v>-5.19584</v>
       </c>
     </row>
     <row r="5">
@@ -1267,16 +1261,16 @@
         </is>
       </c>
       <c r="B5" t="n">
-        <v>5.433042</v>
+        <v>5.302168</v>
       </c>
       <c r="C5" t="n">
-        <v>0.034347</v>
+        <v>0.033653</v>
       </c>
       <c r="D5" t="n">
         <v>2085</v>
       </c>
       <c r="E5" t="n">
-        <v>-0.856122</v>
+        <v>-1.096894</v>
       </c>
     </row>
     <row r="6">
@@ -1286,16 +1280,16 @@
         </is>
       </c>
       <c r="B6" t="n">
-        <v>5.027166</v>
+        <v>4.780053</v>
       </c>
       <c r="C6" t="n">
-        <v>0.031781</v>
+        <v>0.030339</v>
       </c>
       <c r="D6" t="n">
         <v>1374</v>
       </c>
       <c r="E6" t="n">
-        <v>4.113557</v>
+        <v>3.931998</v>
       </c>
     </row>
     <row r="7">
@@ -1305,111 +1299,111 @@
         </is>
       </c>
       <c r="B7" t="n">
-        <v>4.773536</v>
+        <v>4.702895</v>
       </c>
       <c r="C7" t="n">
-        <v>0.030177</v>
+        <v>0.02985</v>
       </c>
       <c r="D7" t="n">
         <v>1539</v>
       </c>
       <c r="E7" t="n">
-        <v>3.544515</v>
+        <v>3.45854</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>岗位细分类集合=人工智能</t>
+          <t>文本SVD4</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>4.200456</v>
+        <v>4.091221</v>
       </c>
       <c r="C8" t="n">
-        <v>0.026555</v>
+        <v>0.025967</v>
       </c>
       <c r="D8" t="n">
-        <v>200</v>
+        <v>970</v>
       </c>
       <c r="E8" t="n">
-        <v>20.21463</v>
+        <v>4.719853</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>文本SVD4</t>
+          <t>学历等级</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>4.121337</v>
+        <v>3.754676</v>
       </c>
       <c r="C9" t="n">
-        <v>0.026054</v>
+        <v>0.023831</v>
       </c>
       <c r="D9" t="n">
-        <v>969</v>
+        <v>1934</v>
       </c>
       <c r="E9" t="n">
-        <v>4.716519</v>
+        <v>-0.810607</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>文本SVD5</t>
+          <t>文本SVD2</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>3.811497</v>
+        <v>3.719439</v>
       </c>
       <c r="C10" t="n">
-        <v>0.024096</v>
+        <v>0.023608</v>
       </c>
       <c r="D10" t="n">
-        <v>1003</v>
+        <v>985</v>
       </c>
       <c r="E10" t="n">
-        <v>-3.779334</v>
+        <v>-3.560242</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>文本SVD2</t>
+          <t>岗位细分类集合=人工智能</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>3.776653</v>
+        <v>3.629611</v>
       </c>
       <c r="C11" t="n">
-        <v>0.023875</v>
+        <v>0.023038</v>
       </c>
       <c r="D11" t="n">
-        <v>985</v>
+        <v>200</v>
       </c>
       <c r="E11" t="n">
-        <v>-3.478788</v>
+        <v>17.191847</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>学历等级</t>
+          <t>文本SVD5</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>3.575971</v>
+        <v>3.595704</v>
       </c>
       <c r="C12" t="n">
-        <v>0.022607</v>
+        <v>0.022822</v>
       </c>
       <c r="D12" t="n">
-        <v>1934</v>
+        <v>1003</v>
       </c>
       <c r="E12" t="n">
-        <v>-0.6732050000000001</v>
+        <v>-3.540099</v>
       </c>
     </row>
     <row r="13">
@@ -1419,16 +1413,16 @@
         </is>
       </c>
       <c r="B13" t="n">
-        <v>3.34792</v>
+        <v>3.424103</v>
       </c>
       <c r="C13" t="n">
-        <v>0.021165</v>
+        <v>0.021733</v>
       </c>
       <c r="D13" t="n">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="E13" t="n">
-        <v>-3.215762</v>
+        <v>-3.379037</v>
       </c>
     </row>
     <row r="14">
@@ -1438,16 +1432,16 @@
         </is>
       </c>
       <c r="B14" t="n">
-        <v>3.043902</v>
+        <v>3.085623</v>
       </c>
       <c r="C14" t="n">
-        <v>0.019243</v>
+        <v>0.019585</v>
       </c>
       <c r="D14" t="n">
         <v>1111</v>
       </c>
       <c r="E14" t="n">
-        <v>3.052286</v>
+        <v>3.068595</v>
       </c>
     </row>
     <row r="15">
@@ -1457,16 +1451,16 @@
         </is>
       </c>
       <c r="B15" t="n">
-        <v>2.723848</v>
+        <v>2.685282</v>
       </c>
       <c r="C15" t="n">
-        <v>0.01722</v>
+        <v>0.017044</v>
       </c>
       <c r="D15" t="n">
         <v>149</v>
       </c>
       <c r="E15" t="n">
-        <v>20.37062</v>
+        <v>19.681614</v>
       </c>
     </row>
     <row r="16">
@@ -1476,16 +1470,16 @@
         </is>
       </c>
       <c r="B16" t="n">
-        <v>2.393149</v>
+        <v>2.570484</v>
       </c>
       <c r="C16" t="n">
-        <v>0.015129</v>
+        <v>0.016315</v>
       </c>
       <c r="D16" t="n">
         <v>2233</v>
       </c>
       <c r="E16" t="n">
-        <v>-0.06637700000000001</v>
+        <v>-0.09597700000000001</v>
       </c>
     </row>
   </sheetData>
@@ -1542,10 +1536,10 @@
         <v>74</v>
       </c>
       <c r="D2" t="n">
-        <v>22.910199</v>
+        <v>21.380193</v>
       </c>
       <c r="E2" t="n">
-        <v>1.76088</v>
+        <v>1.725676</v>
       </c>
     </row>
     <row r="3">
@@ -1561,10 +1555,10 @@
         <v>15</v>
       </c>
       <c r="D3" t="n">
-        <v>41.801341</v>
+        <v>45.147953</v>
       </c>
       <c r="E3" t="n">
-        <v>0.602917</v>
+        <v>0.608919</v>
       </c>
     </row>
     <row r="4">
@@ -1580,10 +1574,10 @@
         <v>259</v>
       </c>
       <c r="D4" t="n">
-        <v>-1.002237</v>
+        <v>-1.84764</v>
       </c>
       <c r="E4" t="n">
-        <v>0.407285</v>
+        <v>0.523756</v>
       </c>
     </row>
     <row r="5">
@@ -1599,29 +1593,29 @@
         <v>80</v>
       </c>
       <c r="D5" t="n">
-        <v>4.691634</v>
+        <v>4.736397</v>
       </c>
       <c r="E5" t="n">
-        <v>0.370409</v>
+        <v>0.365411</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>办公软件</t>
+          <t>数据分析</t>
         </is>
       </c>
       <c r="B6" t="n">
-        <v>2591</v>
+        <v>2718</v>
       </c>
       <c r="C6" t="n">
-        <v>361</v>
+        <v>402</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.707606</v>
+        <v>-0.844594</v>
       </c>
       <c r="E6" t="n">
-        <v>0.285662</v>
+        <v>0.361914</v>
       </c>
     </row>
     <row r="7">
@@ -1637,295 +1631,295 @@
         <v>61</v>
       </c>
       <c r="D7" t="n">
-        <v>4.814829</v>
+        <v>6.262866</v>
       </c>
       <c r="E7" t="n">
-        <v>0.274671</v>
+        <v>0.324723</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Java</t>
+          <t>深度学习</t>
         </is>
       </c>
       <c r="B8" t="n">
-        <v>619</v>
+        <v>572</v>
       </c>
       <c r="C8" t="n">
-        <v>85</v>
+        <v>74</v>
       </c>
       <c r="D8" t="n">
-        <v>-2.697057</v>
+        <v>0.721616</v>
       </c>
       <c r="E8" t="n">
-        <v>0.245455</v>
+        <v>0.210262</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>项目管理</t>
+          <t>Java</t>
         </is>
       </c>
       <c r="B9" t="n">
-        <v>487</v>
+        <v>619</v>
       </c>
       <c r="C9" t="n">
-        <v>77</v>
+        <v>85</v>
       </c>
       <c r="D9" t="n">
-        <v>3.673901</v>
+        <v>-2.270896</v>
       </c>
       <c r="E9" t="n">
-        <v>0.228526</v>
+        <v>0.205964</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>数据分析</t>
+          <t>项目管理</t>
         </is>
       </c>
       <c r="B10" t="n">
-        <v>2718</v>
+        <v>487</v>
       </c>
       <c r="C10" t="n">
-        <v>402</v>
+        <v>77</v>
       </c>
       <c r="D10" t="n">
-        <v>-0.610657</v>
+        <v>2.803566</v>
       </c>
       <c r="E10" t="n">
-        <v>0.201132</v>
+        <v>0.171546</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>深度学习</t>
+          <t>NLP</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>572</v>
+        <v>179</v>
       </c>
       <c r="C11" t="n">
-        <v>74</v>
+        <v>18</v>
       </c>
       <c r="D11" t="n">
-        <v>-0.472882</v>
+        <v>6.350753</v>
       </c>
       <c r="E11" t="n">
-        <v>0.180905</v>
+        <v>0.12636</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>NLP</t>
+          <t>计算机视觉</t>
         </is>
       </c>
       <c r="B12" t="n">
-        <v>179</v>
+        <v>295</v>
       </c>
       <c r="C12" t="n">
-        <v>18</v>
+        <v>40</v>
       </c>
       <c r="D12" t="n">
-        <v>6.855472</v>
+        <v>3.436091</v>
       </c>
       <c r="E12" t="n">
-        <v>0.173304</v>
+        <v>0.123726</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>多模态</t>
+          <t>C</t>
         </is>
       </c>
       <c r="B13" t="n">
-        <v>231</v>
+        <v>446</v>
       </c>
       <c r="C13" t="n">
-        <v>27</v>
+        <v>65</v>
       </c>
       <c r="D13" t="n">
-        <v>2.742308</v>
+        <v>1.649561</v>
       </c>
       <c r="E13" t="n">
-        <v>0.155267</v>
+        <v>0.105815</v>
       </c>
     </row>
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>计算机视觉</t>
+          <t>多模态</t>
         </is>
       </c>
       <c r="B14" t="n">
-        <v>295</v>
+        <v>231</v>
       </c>
       <c r="C14" t="n">
-        <v>40</v>
+        <v>27</v>
       </c>
       <c r="D14" t="n">
-        <v>3.154364</v>
+        <v>0.549363</v>
       </c>
       <c r="E14" t="n">
-        <v>0.129567</v>
+        <v>0.09827</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Prompt Engineering</t>
+          <t>大模型</t>
         </is>
       </c>
       <c r="B15" t="n">
-        <v>202</v>
+        <v>866</v>
       </c>
       <c r="C15" t="n">
-        <v>30</v>
+        <v>125</v>
       </c>
       <c r="D15" t="n">
-        <v>-4.294281</v>
+        <v>0.810434</v>
       </c>
       <c r="E15" t="n">
-        <v>0.106327</v>
+        <v>0.09682399999999999</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>C</t>
+          <t>办公软件</t>
         </is>
       </c>
       <c r="B16" t="n">
-        <v>446</v>
+        <v>2591</v>
       </c>
       <c r="C16" t="n">
-        <v>65</v>
+        <v>361</v>
       </c>
       <c r="D16" t="n">
-        <v>1.452553</v>
+        <v>-0.190814</v>
       </c>
       <c r="E16" t="n">
-        <v>0.104653</v>
+        <v>0.081016</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>大数据</t>
+          <t>Agent</t>
         </is>
       </c>
       <c r="B17" t="n">
-        <v>301</v>
+        <v>238</v>
       </c>
       <c r="C17" t="n">
-        <v>49</v>
+        <v>35</v>
       </c>
       <c r="D17" t="n">
-        <v>-2.430318</v>
+        <v>3.029365</v>
       </c>
       <c r="E17" t="n">
-        <v>0.10042</v>
+        <v>0.078837</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>大模型</t>
+          <t>大数据</t>
         </is>
       </c>
       <c r="B18" t="n">
-        <v>866</v>
+        <v>301</v>
       </c>
       <c r="C18" t="n">
-        <v>125</v>
+        <v>49</v>
       </c>
       <c r="D18" t="n">
-        <v>0.585608</v>
+        <v>-1.788325</v>
       </c>
       <c r="E18" t="n">
-        <v>0.071897</v>
+        <v>0.069852</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>MATLAB</t>
+          <t>数据科学</t>
         </is>
       </c>
       <c r="B19" t="n">
-        <v>118</v>
+        <v>205</v>
       </c>
       <c r="C19" t="n">
-        <v>15</v>
+        <v>29</v>
       </c>
       <c r="D19" t="n">
-        <v>4.45055</v>
+        <v>2.809429</v>
       </c>
       <c r="E19" t="n">
-        <v>0.059554</v>
+        <v>0.06837600000000001</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>AIGC</t>
+          <t>人工智能</t>
         </is>
       </c>
       <c r="B20" t="n">
-        <v>313</v>
+        <v>2418</v>
       </c>
       <c r="C20" t="n">
-        <v>41</v>
+        <v>374</v>
       </c>
       <c r="D20" t="n">
-        <v>-1.405586</v>
+        <v>0.098874</v>
       </c>
       <c r="E20" t="n">
-        <v>0.058098</v>
+        <v>0.056108</v>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Agent</t>
+          <t>产品设计</t>
         </is>
       </c>
       <c r="B21" t="n">
-        <v>238</v>
+        <v>484</v>
       </c>
       <c r="C21" t="n">
-        <v>35</v>
+        <v>70</v>
       </c>
       <c r="D21" t="n">
-        <v>1.850183</v>
+        <v>0.8492150000000001</v>
       </c>
       <c r="E21" t="n">
-        <v>0.056671</v>
+        <v>0.054547</v>
       </c>
     </row>
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>产品设计</t>
+          <t>原型设计</t>
         </is>
       </c>
       <c r="B22" t="n">
-        <v>484</v>
+        <v>445</v>
       </c>
       <c r="C22" t="n">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="D22" t="n">
-        <v>0.762679</v>
+        <v>0.846513</v>
       </c>
       <c r="E22" t="n">
-        <v>0.054739</v>
+        <v>0.053749</v>
       </c>
     </row>
     <row r="23">
@@ -1941,295 +1935,295 @@
         <v>37</v>
       </c>
       <c r="D23" t="n">
-        <v>1.736432</v>
+        <v>1.5936</v>
       </c>
       <c r="E23" t="n">
-        <v>0.054161</v>
+        <v>0.048469</v>
       </c>
     </row>
     <row r="24">
       <c r="A24" t="inlineStr">
         <is>
-          <t>TensorFlow</t>
+          <t>SQL</t>
         </is>
       </c>
       <c r="B24" t="n">
-        <v>277</v>
+        <v>1387</v>
       </c>
       <c r="C24" t="n">
-        <v>36</v>
+        <v>208</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.733595</v>
+        <v>0.188291</v>
       </c>
       <c r="E24" t="n">
-        <v>0.052019</v>
+        <v>0.046979</v>
       </c>
     </row>
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Git</t>
+          <t>Spark</t>
         </is>
       </c>
       <c r="B25" t="n">
-        <v>235</v>
+        <v>115</v>
       </c>
       <c r="C25" t="n">
-        <v>34</v>
+        <v>13</v>
       </c>
       <c r="D25" t="n">
-        <v>1.579842</v>
+        <v>3.003416</v>
       </c>
       <c r="E25" t="n">
-        <v>0.051998</v>
+        <v>0.046541</v>
       </c>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Spark</t>
+          <t>MATLAB</t>
         </is>
       </c>
       <c r="B26" t="n">
-        <v>115</v>
+        <v>118</v>
       </c>
       <c r="C26" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="D26" t="n">
-        <v>3.122355</v>
+        <v>2.81403</v>
       </c>
       <c r="E26" t="n">
-        <v>0.050306</v>
+        <v>0.046058</v>
       </c>
     </row>
     <row r="27">
       <c r="A27" t="inlineStr">
         <is>
-          <t>人工智能</t>
+          <t>Prompt Engineering</t>
         </is>
       </c>
       <c r="B27" t="n">
-        <v>2418</v>
+        <v>202</v>
       </c>
       <c r="C27" t="n">
-        <v>374</v>
+        <v>30</v>
       </c>
       <c r="D27" t="n">
-        <v>-0.10739</v>
+        <v>-1.866092</v>
       </c>
       <c r="E27" t="n">
-        <v>0.048397</v>
+        <v>0.045131</v>
       </c>
     </row>
     <row r="28">
       <c r="A28" t="inlineStr">
         <is>
-          <t>数据科学</t>
+          <t>HTML</t>
         </is>
       </c>
       <c r="B28" t="n">
-        <v>205</v>
+        <v>162</v>
       </c>
       <c r="C28" t="n">
-        <v>29</v>
+        <v>26</v>
       </c>
       <c r="D28" t="n">
-        <v>2.041054</v>
+        <v>2.397954</v>
       </c>
       <c r="E28" t="n">
-        <v>0.045097</v>
+        <v>0.041583</v>
       </c>
     </row>
     <row r="29">
       <c r="A29" t="inlineStr">
         <is>
-          <t>SQL</t>
+          <t>TensorFlow</t>
         </is>
       </c>
       <c r="B29" t="n">
-        <v>1387</v>
+        <v>277</v>
       </c>
       <c r="C29" t="n">
-        <v>208</v>
+        <v>36</v>
       </c>
       <c r="D29" t="n">
-        <v>0.186899</v>
+        <v>-1.154598</v>
       </c>
       <c r="E29" t="n">
-        <v>0.044681</v>
+        <v>0.040897</v>
       </c>
     </row>
     <row r="30">
       <c r="A30" t="inlineStr">
         <is>
-          <t>HTML</t>
+          <t>Git</t>
         </is>
       </c>
       <c r="B30" t="n">
-        <v>162</v>
+        <v>235</v>
       </c>
       <c r="C30" t="n">
-        <v>26</v>
+        <v>34</v>
       </c>
       <c r="D30" t="n">
-        <v>2.048257</v>
+        <v>1.212535</v>
       </c>
       <c r="E30" t="n">
-        <v>0.038385</v>
+        <v>0.039819</v>
       </c>
     </row>
     <row r="31">
       <c r="A31" t="inlineStr">
         <is>
-          <t>Excel</t>
+          <t>Vue</t>
         </is>
       </c>
       <c r="B31" t="n">
-        <v>2737</v>
+        <v>140</v>
       </c>
       <c r="C31" t="n">
-        <v>426</v>
+        <v>22</v>
       </c>
       <c r="D31" t="n">
-        <v>-0.064752</v>
+        <v>-2.444467</v>
       </c>
       <c r="E31" t="n">
-        <v>0.038338</v>
+        <v>0.038965</v>
       </c>
     </row>
     <row r="32">
       <c r="A32" t="inlineStr">
         <is>
-          <t>数据挖掘</t>
+          <t>Excel</t>
         </is>
       </c>
       <c r="B32" t="n">
-        <v>156</v>
+        <v>2737</v>
       </c>
       <c r="C32" t="n">
-        <v>24</v>
+        <v>426</v>
       </c>
       <c r="D32" t="n">
-        <v>2.003964</v>
+        <v>-0.056578</v>
       </c>
       <c r="E32" t="n">
-        <v>0.035425</v>
+        <v>0.038748</v>
       </c>
     </row>
     <row r="33">
       <c r="A33" t="inlineStr">
         <is>
-          <t>原型设计</t>
+          <t>AIGC</t>
         </is>
       </c>
       <c r="B33" t="n">
-        <v>445</v>
+        <v>313</v>
       </c>
       <c r="C33" t="n">
-        <v>69</v>
+        <v>41</v>
       </c>
       <c r="D33" t="n">
-        <v>0.473324</v>
+        <v>-0.523139</v>
       </c>
       <c r="E33" t="n">
-        <v>0.031416</v>
+        <v>0.033534</v>
       </c>
     </row>
     <row r="34">
       <c r="A34" t="inlineStr">
         <is>
-          <t>市场调研</t>
+          <t>微调</t>
         </is>
       </c>
       <c r="B34" t="n">
-        <v>437</v>
+        <v>132</v>
       </c>
       <c r="C34" t="n">
-        <v>57</v>
+        <v>16</v>
       </c>
       <c r="D34" t="n">
-        <v>-0.4308</v>
+        <v>1.641399</v>
       </c>
       <c r="E34" t="n">
-        <v>0.023842</v>
+        <v>0.031374</v>
       </c>
     </row>
     <row r="35">
       <c r="A35" t="inlineStr">
         <is>
-          <t>JavaScript</t>
+          <t>市场调研</t>
         </is>
       </c>
       <c r="B35" t="n">
-        <v>210</v>
+        <v>437</v>
       </c>
       <c r="C35" t="n">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="D35" t="n">
-        <v>-0.741443</v>
+        <v>-0.522798</v>
       </c>
       <c r="E35" t="n">
-        <v>0.023508</v>
+        <v>0.028559</v>
       </c>
     </row>
     <row r="36">
       <c r="A36" t="inlineStr">
         <is>
-          <t>MySQL</t>
+          <t>Power BI</t>
         </is>
       </c>
       <c r="B36" t="n">
-        <v>266</v>
+        <v>152</v>
       </c>
       <c r="C36" t="n">
-        <v>43</v>
+        <v>20</v>
       </c>
       <c r="D36" t="n">
-        <v>0.241472</v>
+        <v>1.013909</v>
       </c>
       <c r="E36" t="n">
-        <v>0.019455</v>
+        <v>0.027348</v>
       </c>
     </row>
     <row r="37">
       <c r="A37" t="inlineStr">
         <is>
-          <t>微调</t>
+          <t>MySQL</t>
         </is>
       </c>
       <c r="B37" t="n">
-        <v>132</v>
+        <v>266</v>
       </c>
       <c r="C37" t="n">
-        <v>16</v>
+        <v>43</v>
       </c>
       <c r="D37" t="n">
-        <v>0.734278</v>
+        <v>0.604704</v>
       </c>
       <c r="E37" t="n">
-        <v>0.019239</v>
+        <v>0.022975</v>
       </c>
     </row>
     <row r="38">
       <c r="A38" t="inlineStr">
         <is>
-          <t>Vue</t>
+          <t>Word</t>
         </is>
       </c>
       <c r="B38" t="n">
-        <v>140</v>
+        <v>599</v>
       </c>
       <c r="C38" t="n">
-        <v>22</v>
+        <v>84</v>
       </c>
       <c r="D38" t="n">
-        <v>-1.016467</v>
+        <v>0.248595</v>
       </c>
       <c r="E38" t="n">
-        <v>0.018456</v>
+        <v>0.021342</v>
       </c>
     </row>
     <row r="39">
@@ -2245,48 +2239,48 @@
         <v>52</v>
       </c>
       <c r="D39" t="n">
-        <v>-0.057313</v>
+        <v>-0.148701</v>
       </c>
       <c r="E39" t="n">
-        <v>0.015495</v>
+        <v>0.021112</v>
       </c>
     </row>
     <row r="40">
       <c r="A40" t="inlineStr">
         <is>
-          <t>内容运营</t>
+          <t>单元测试</t>
         </is>
       </c>
       <c r="B40" t="n">
-        <v>774</v>
+        <v>123</v>
       </c>
       <c r="C40" t="n">
-        <v>111</v>
+        <v>19</v>
       </c>
       <c r="D40" t="n">
-        <v>0.149377</v>
+        <v>-1.289597</v>
       </c>
       <c r="E40" t="n">
-        <v>0.013209</v>
+        <v>0.018956</v>
       </c>
     </row>
     <row r="41">
       <c r="A41" t="inlineStr">
         <is>
-          <t>用户研究</t>
+          <t>数据挖掘</t>
         </is>
       </c>
       <c r="B41" t="n">
-        <v>383</v>
+        <v>156</v>
       </c>
       <c r="C41" t="n">
-        <v>61</v>
+        <v>24</v>
       </c>
       <c r="D41" t="n">
-        <v>0.21443</v>
+        <v>0.121996</v>
       </c>
       <c r="E41" t="n">
-        <v>0.012858</v>
+        <v>0.017981</v>
       </c>
     </row>
     <row r="42">
@@ -2302,86 +2296,86 @@
         <v>200</v>
       </c>
       <c r="D42" t="n">
-        <v>-0.019068</v>
+        <v>-0.040771</v>
       </c>
       <c r="E42" t="n">
-        <v>0.01086</v>
+        <v>0.017453</v>
       </c>
     </row>
     <row r="43">
       <c r="A43" t="inlineStr">
         <is>
-          <t>Word</t>
+          <t>JavaScript</t>
         </is>
       </c>
       <c r="B43" t="n">
-        <v>599</v>
+        <v>210</v>
       </c>
       <c r="C43" t="n">
-        <v>84</v>
+        <v>36</v>
       </c>
       <c r="D43" t="n">
-        <v>0.133505</v>
+        <v>-0.689343</v>
       </c>
       <c r="E43" t="n">
-        <v>0.009528999999999999</v>
+        <v>0.016438</v>
       </c>
     </row>
     <row r="44">
       <c r="A44" t="inlineStr">
         <is>
-          <t>数据可视化</t>
+          <t>用户研究</t>
         </is>
       </c>
       <c r="B44" t="n">
-        <v>409</v>
+        <v>383</v>
       </c>
       <c r="C44" t="n">
-        <v>67</v>
+        <v>61</v>
       </c>
       <c r="D44" t="n">
-        <v>0.12837</v>
+        <v>0.259956</v>
       </c>
       <c r="E44" t="n">
-        <v>0.007997000000000001</v>
+        <v>0.015116</v>
       </c>
     </row>
     <row r="45">
       <c r="A45" t="inlineStr">
         <is>
-          <t>RAG</t>
+          <t>内容运营</t>
         </is>
       </c>
       <c r="B45" t="n">
-        <v>110</v>
+        <v>774</v>
       </c>
       <c r="C45" t="n">
-        <v>10</v>
+        <v>111</v>
       </c>
       <c r="D45" t="n">
-        <v>0.594403</v>
+        <v>0.134654</v>
       </c>
       <c r="E45" t="n">
-        <v>0.007592</v>
+        <v>0.012448</v>
       </c>
     </row>
     <row r="46">
       <c r="A46" t="inlineStr">
         <is>
-          <t>React</t>
+          <t>数据可视化</t>
         </is>
       </c>
       <c r="B46" t="n">
-        <v>126</v>
+        <v>409</v>
       </c>
       <c r="C46" t="n">
-        <v>23</v>
+        <v>67</v>
       </c>
       <c r="D46" t="n">
-        <v>-0.384752</v>
+        <v>0.173359</v>
       </c>
       <c r="E46" t="n">
-        <v>0.005533</v>
+        <v>0.011326</v>
       </c>
     </row>
     <row r="47">
@@ -2397,80 +2391,80 @@
         <v>43</v>
       </c>
       <c r="D47" t="n">
-        <v>0.037827</v>
+        <v>0.185257</v>
       </c>
       <c r="E47" t="n">
-        <v>0.001675</v>
+        <v>0.008045</v>
       </c>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>CSS</t>
+          <t>RAG</t>
         </is>
       </c>
       <c r="B48" t="n">
-        <v>143</v>
+        <v>110</v>
       </c>
       <c r="C48" t="n">
-        <v>22</v>
+        <v>10</v>
       </c>
       <c r="D48" t="n">
-        <v>0</v>
+        <v>-0.638734</v>
       </c>
       <c r="E48" t="n">
-        <v>0</v>
+        <v>0.007741</v>
       </c>
     </row>
     <row r="49">
       <c r="A49" t="inlineStr">
         <is>
-          <t>Power BI</t>
+          <t>Tableau</t>
         </is>
       </c>
       <c r="B49" t="n">
-        <v>152</v>
+        <v>165</v>
       </c>
       <c r="C49" t="n">
-        <v>20</v>
+        <v>25</v>
       </c>
       <c r="D49" t="n">
-        <v>0</v>
+        <v>0.165787</v>
       </c>
       <c r="E49" t="n">
-        <v>0</v>
+        <v>0.003893</v>
       </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t>Tableau</t>
+          <t>React</t>
         </is>
       </c>
       <c r="B50" t="n">
-        <v>165</v>
+        <v>126</v>
       </c>
       <c r="C50" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="D50" t="n">
-        <v>0</v>
+        <v>-0.225473</v>
       </c>
       <c r="E50" t="n">
-        <v>0</v>
+        <v>0.003183</v>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t>单元测试</t>
+          <t>CSS</t>
         </is>
       </c>
       <c r="B51" t="n">
-        <v>123</v>
+        <v>143</v>
       </c>
       <c r="C51" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="D51" t="n">
         <v>0</v>
@@ -2788,22 +2782,22 @@
         <v>232</v>
       </c>
       <c r="C4" t="n">
-        <v>36.190873</v>
+        <v>36.51492</v>
       </c>
       <c r="D4" t="n">
-        <v>69.87125899999999</v>
+        <v>71.21809500000001</v>
       </c>
       <c r="E4" t="n">
-        <v>0.5896709999999999</v>
+        <v>0.5737</v>
       </c>
       <c r="F4" t="n">
-        <v>35.968386</v>
+        <v>36.224869</v>
       </c>
       <c r="G4" t="n">
-        <v>65.953063</v>
+        <v>66.197988</v>
       </c>
       <c r="H4" t="n">
-        <v>0.567337</v>
+        <v>0.564117</v>
       </c>
       <c r="I4" t="n">
         <v>10418</v>
@@ -2825,22 +2819,22 @@
         <v>288</v>
       </c>
       <c r="C5" t="n">
-        <v>36.635124</v>
+        <v>36.038993</v>
       </c>
       <c r="D5" t="n">
-        <v>70.771012</v>
+        <v>69.9654</v>
       </c>
       <c r="E5" t="n">
-        <v>0.579035</v>
+        <v>0.588565</v>
       </c>
       <c r="F5" t="n">
-        <v>36.453256</v>
+        <v>35.996481</v>
       </c>
       <c r="G5" t="n">
-        <v>67.24848</v>
+        <v>66.29566699999999</v>
       </c>
       <c r="H5" t="n">
-        <v>0.5501740000000001</v>
+        <v>0.5628300000000001</v>
       </c>
       <c r="I5" t="n">
         <v>10418</v>
@@ -2862,22 +2856,22 @@
         <v>290</v>
       </c>
       <c r="C6" t="n">
-        <v>36.258904</v>
+        <v>36.126096</v>
       </c>
       <c r="D6" t="n">
-        <v>69.909462</v>
+        <v>69.77090800000001</v>
       </c>
       <c r="E6" t="n">
-        <v>0.589222</v>
+        <v>0.590849</v>
       </c>
       <c r="F6" t="n">
-        <v>36.417074</v>
+        <v>36.396036</v>
       </c>
       <c r="G6" t="n">
-        <v>67.001621</v>
+        <v>66.949583</v>
       </c>
       <c r="H6" t="n">
-        <v>0.55347</v>
+        <v>0.554163</v>
       </c>
       <c r="I6" t="n">
         <v>10418</v>
@@ -2972,19 +2966,19 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>36.635124</v>
+        <v>36.038993</v>
       </c>
       <c r="E2" t="n">
-        <v>36.258904</v>
+        <v>36.126096</v>
       </c>
       <c r="F2" t="n">
-        <v>0.37622</v>
+        <v>-0.087103</v>
       </c>
       <c r="G2" t="n">
-        <v>-0.053566</v>
+        <v>-0.557664</v>
       </c>
       <c r="H2" t="n">
-        <v>0.793957</v>
+        <v>0.407551</v>
       </c>
       <c r="I2" t="inlineStr">
         <is>
@@ -3012,19 +3006,19 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>36.453256</v>
+        <v>35.996481</v>
       </c>
       <c r="E3" t="n">
-        <v>36.417074</v>
+        <v>36.396036</v>
       </c>
       <c r="F3" t="n">
-        <v>0.036182</v>
+        <v>-0.399554</v>
       </c>
       <c r="G3" t="n">
-        <v>-0.419526</v>
+        <v>-0.863312</v>
       </c>
       <c r="H3" t="n">
-        <v>0.471827</v>
+        <v>0.056279</v>
       </c>
       <c r="I3" t="inlineStr">
         <is>
@@ -3135,16 +3129,16 @@
         <v>36.449958</v>
       </c>
       <c r="E6" t="n">
-        <v>36.190873</v>
+        <v>36.51492</v>
       </c>
       <c r="F6" t="n">
-        <v>0.259085</v>
+        <v>-0.06496200000000001</v>
       </c>
       <c r="G6" t="n">
-        <v>-0.806226</v>
+        <v>-1.149532</v>
       </c>
       <c r="H6" t="n">
-        <v>1.398121</v>
+        <v>1.124648</v>
       </c>
       <c r="I6" t="inlineStr">
         <is>
@@ -3175,16 +3169,16 @@
         <v>34.712727</v>
       </c>
       <c r="E7" t="n">
-        <v>35.968386</v>
+        <v>36.224869</v>
       </c>
       <c r="F7" t="n">
-        <v>-1.255659</v>
+        <v>-1.512142</v>
       </c>
       <c r="G7" t="n">
-        <v>-2.266797</v>
+        <v>-2.542551</v>
       </c>
       <c r="H7" t="n">
-        <v>-0.187017</v>
+        <v>-0.490906</v>
       </c>
       <c r="I7" t="inlineStr">
         <is>
@@ -3215,16 +3209,16 @@
         <v>36.449958</v>
       </c>
       <c r="E8" t="n">
-        <v>36.635124</v>
+        <v>36.038993</v>
       </c>
       <c r="F8" t="n">
-        <v>-0.185166</v>
+        <v>0.410965</v>
       </c>
       <c r="G8" t="n">
-        <v>-1.298019</v>
+        <v>-0.709811</v>
       </c>
       <c r="H8" t="n">
-        <v>0.980715</v>
+        <v>1.659958</v>
       </c>
       <c r="I8" t="inlineStr">
         <is>
@@ -3255,16 +3249,16 @@
         <v>34.712727</v>
       </c>
       <c r="E9" t="n">
-        <v>36.453256</v>
+        <v>35.996481</v>
       </c>
       <c r="F9" t="n">
-        <v>-1.740529</v>
+        <v>-1.283754</v>
       </c>
       <c r="G9" t="n">
-        <v>-2.838029</v>
+        <v>-2.397711</v>
       </c>
       <c r="H9" t="n">
-        <v>-0.6043500000000001</v>
+        <v>-0.275467</v>
       </c>
       <c r="I9" t="inlineStr">
         <is>
@@ -3343,22 +3337,22 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.635124</v>
+        <v>36.038993</v>
       </c>
       <c r="D2" t="n">
-        <v>70.771012</v>
+        <v>69.9654</v>
       </c>
       <c r="E2" t="n">
-        <v>0.579035</v>
+        <v>0.588565</v>
       </c>
       <c r="F2" t="n">
-        <v>36.453256</v>
+        <v>35.996481</v>
       </c>
       <c r="G2" t="n">
-        <v>67.24848</v>
+        <v>66.29566699999999</v>
       </c>
       <c r="H2" t="n">
-        <v>0.5501740000000001</v>
+        <v>0.5628300000000001</v>
       </c>
     </row>
     <row r="3">
@@ -3373,22 +3367,22 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.709331</v>
+        <v>36.872254</v>
       </c>
       <c r="D3" t="n">
-        <v>69.01518299999999</v>
+        <v>68.684195</v>
       </c>
       <c r="E3" t="n">
-        <v>0.599664</v>
+        <v>0.603495</v>
       </c>
       <c r="F3" t="n">
-        <v>36.374433</v>
+        <v>36.610101</v>
       </c>
       <c r="G3" t="n">
-        <v>65.219776</v>
+        <v>65.638513</v>
       </c>
       <c r="H3" t="n">
-        <v>0.576904</v>
+        <v>0.571454</v>
       </c>
     </row>
     <row r="4">
@@ -3403,22 +3397,22 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>38.232707</v>
+        <v>38.146395</v>
       </c>
       <c r="D4" t="n">
-        <v>74.244028</v>
+        <v>73.747653</v>
       </c>
       <c r="E4" t="n">
-        <v>0.536705</v>
+        <v>0.542879</v>
       </c>
       <c r="F4" t="n">
-        <v>37.050243</v>
+        <v>37.069057</v>
       </c>
       <c r="G4" t="n">
-        <v>68.836217</v>
+        <v>69.085273</v>
       </c>
       <c r="H4" t="n">
-        <v>0.528682</v>
+        <v>0.525265</v>
       </c>
     </row>
     <row r="5">
@@ -3433,22 +3427,22 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>45.307314</v>
+        <v>45.30729</v>
       </c>
       <c r="D5" t="n">
-        <v>85.69301400000001</v>
+        <v>85.69307000000001</v>
       </c>
       <c r="E5" t="n">
         <v>0.3828</v>
       </c>
       <c r="F5" t="n">
-        <v>43.739362</v>
+        <v>43.739258</v>
       </c>
       <c r="G5" t="n">
-        <v>77.430978</v>
+        <v>77.43084500000001</v>
       </c>
       <c r="H5" t="n">
-        <v>0.403639</v>
+        <v>0.403641</v>
       </c>
     </row>
     <row r="6">
@@ -3564,13 +3558,13 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.453256</v>
+        <v>35.996481</v>
       </c>
       <c r="C2" t="n">
-        <v>67.24848</v>
+        <v>66.29566699999999</v>
       </c>
       <c r="D2" t="n">
-        <v>0.5501740000000001</v>
+        <v>0.5628300000000001</v>
       </c>
       <c r="E2" t="n">
         <v>2233</v>
@@ -3586,13 +3580,13 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.301511</v>
+        <v>35.476021</v>
       </c>
       <c r="C3" t="n">
-        <v>64.440247</v>
+        <v>64.80933400000001</v>
       </c>
       <c r="D3" t="n">
-        <v>0.586958</v>
+        <v>0.582213</v>
       </c>
       <c r="E3" t="n">
         <v>2233</v>
@@ -3657,10 +3651,10 @@
         <v>2233</v>
       </c>
       <c r="D2" t="n">
-        <v>35.301511</v>
+        <v>35.476021</v>
       </c>
       <c r="E2" t="n">
-        <v>64.440247</v>
+        <v>64.80933400000001</v>
       </c>
     </row>
     <row r="3">
@@ -3678,10 +3672,10 @@
         <v>628</v>
       </c>
       <c r="D3" t="n">
-        <v>36.016921</v>
+        <v>35.433615</v>
       </c>
       <c r="E3" t="n">
-        <v>49.966743</v>
+        <v>49.039927</v>
       </c>
     </row>
     <row r="4">
@@ -3699,10 +3693,10 @@
         <v>702</v>
       </c>
       <c r="D4" t="n">
-        <v>22.401059</v>
+        <v>22.718336</v>
       </c>
       <c r="E4" t="n">
-        <v>31.18655</v>
+        <v>31.864841</v>
       </c>
     </row>
     <row r="5">
@@ -3720,10 +3714,10 @@
         <v>477</v>
       </c>
       <c r="D5" t="n">
-        <v>28.670529</v>
+        <v>29.407602</v>
       </c>
       <c r="E5" t="n">
-        <v>39.105057</v>
+        <v>40.13135</v>
       </c>
     </row>
     <row r="6">
@@ -3741,10 +3735,10 @@
         <v>426</v>
       </c>
       <c r="D6" t="n">
-        <v>62.930189</v>
+        <v>63.356684</v>
       </c>
       <c r="E6" t="n">
-        <v>121.536766</v>
+        <v>122.454002</v>
       </c>
     </row>
   </sheetData>
@@ -3793,10 +3787,10 @@
         <v>933</v>
       </c>
       <c r="C2" t="n">
-        <v>29.210548</v>
+        <v>29.779193</v>
       </c>
       <c r="D2" t="n">
-        <v>43.586832</v>
+        <v>44.008937</v>
       </c>
     </row>
     <row r="3">
@@ -3809,42 +3803,42 @@
         <v>1493</v>
       </c>
       <c r="C3" t="n">
-        <v>29.464841</v>
+        <v>29.817912</v>
       </c>
       <c r="D3" t="n">
-        <v>43.325227</v>
+        <v>43.766176</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>技术管理</t>
+          <t>游戏</t>
         </is>
       </c>
       <c r="B4" t="n">
-        <v>90</v>
+        <v>120</v>
       </c>
       <c r="C4" t="n">
-        <v>32.382271</v>
+        <v>32.2488</v>
       </c>
       <c r="D4" t="n">
-        <v>44.49019</v>
+        <v>41.036596</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>游戏</t>
+          <t>技术管理</t>
         </is>
       </c>
       <c r="B5" t="n">
-        <v>120</v>
+        <v>90</v>
       </c>
       <c r="C5" t="n">
-        <v>33.572045</v>
+        <v>32.524719</v>
       </c>
       <c r="D5" t="n">
-        <v>43.358692</v>
+        <v>44.458097</v>
       </c>
     </row>
     <row r="6">
@@ -3857,10 +3851,10 @@
         <v>164</v>
       </c>
       <c r="C6" t="n">
-        <v>34.689506</v>
+        <v>32.828397</v>
       </c>
       <c r="D6" t="n">
-        <v>60.017712</v>
+        <v>58.0466</v>
       </c>
     </row>
     <row r="7">
@@ -3873,10 +3867,10 @@
         <v>437</v>
       </c>
       <c r="C7" t="n">
-        <v>49.573358</v>
+        <v>49.8513</v>
       </c>
       <c r="D7" t="n">
-        <v>105.35052</v>
+        <v>105.343391</v>
       </c>
     </row>
     <row r="8">
@@ -3889,10 +3883,10 @@
         <v>499</v>
       </c>
       <c r="C8" t="n">
-        <v>55.645736</v>
+        <v>55.287805</v>
       </c>
       <c r="D8" t="n">
-        <v>109.651422</v>
+        <v>109.878365</v>
       </c>
     </row>
     <row r="9">
@@ -3905,10 +3899,10 @@
         <v>205</v>
       </c>
       <c r="C9" t="n">
-        <v>56.91957</v>
+        <v>56.106477</v>
       </c>
       <c r="D9" t="n">
-        <v>115.128414</v>
+        <v>113.902471</v>
       </c>
     </row>
     <row r="10">
@@ -3921,10 +3915,10 @@
         <v>141</v>
       </c>
       <c r="C10" t="n">
-        <v>57.127111</v>
+        <v>56.218217</v>
       </c>
       <c r="D10" t="n">
-        <v>108.600865</v>
+        <v>107.573772</v>
       </c>
     </row>
     <row r="11">
@@ -3937,10 +3931,10 @@
         <v>363</v>
       </c>
       <c r="C11" t="n">
-        <v>57.361217</v>
+        <v>57.085812</v>
       </c>
       <c r="D11" t="n">
-        <v>110.842032</v>
+        <v>111.557305</v>
       </c>
     </row>
     <row r="12">
@@ -3953,10 +3947,10 @@
         <v>250</v>
       </c>
       <c r="C12" t="n">
-        <v>57.864117</v>
+        <v>57.328417</v>
       </c>
       <c r="D12" t="n">
-        <v>130.106045</v>
+        <v>130.943976</v>
       </c>
     </row>
     <row r="13">
@@ -3969,10 +3963,10 @@
         <v>237</v>
       </c>
       <c r="C13" t="n">
-        <v>60.536126</v>
+        <v>60.212018</v>
       </c>
       <c r="D13" t="n">
-        <v>132.473527</v>
+        <v>133.553675</v>
       </c>
     </row>
   </sheetData>
@@ -4031,16 +4025,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>36.635124</v>
+        <v>36.038993</v>
       </c>
       <c r="D2" t="n">
-        <v>36.453256</v>
+        <v>35.996481</v>
       </c>
       <c r="E2" t="n">
-        <v>67.24848</v>
+        <v>66.29566699999999</v>
       </c>
       <c r="F2" t="n">
-        <v>0.5501740000000001</v>
+        <v>0.5628300000000001</v>
       </c>
     </row>
     <row r="3">
@@ -4053,16 +4047,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>36.709331</v>
+        <v>36.872254</v>
       </c>
       <c r="D3" t="n">
-        <v>36.374433</v>
+        <v>36.610101</v>
       </c>
       <c r="E3" t="n">
-        <v>65.219776</v>
+        <v>65.638513</v>
       </c>
       <c r="F3" t="n">
-        <v>0.576904</v>
+        <v>0.571454</v>
       </c>
     </row>
     <row r="4">
@@ -4075,16 +4069,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>35.052459</v>
+        <v>34.7275</v>
       </c>
       <c r="D4" t="n">
-        <v>35.07521</v>
+        <v>35.330233</v>
       </c>
       <c r="E4" t="n">
-        <v>63.225293</v>
+        <v>63.195894</v>
       </c>
       <c r="F4" t="n">
-        <v>0.588047</v>
+        <v>0.58843</v>
       </c>
     </row>
     <row r="5">
@@ -4097,16 +4091,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>36.079428</v>
+        <v>35.968016</v>
       </c>
       <c r="D5" t="n">
-        <v>36.49674</v>
+        <v>36.632071</v>
       </c>
       <c r="E5" t="n">
-        <v>64.19069399999999</v>
+        <v>64.588768</v>
       </c>
       <c r="F5" t="n">
-        <v>0.57537</v>
+        <v>0.570087</v>
       </c>
     </row>
     <row r="6">
@@ -4119,16 +4113,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>34.287021</v>
+        <v>34.21049</v>
       </c>
       <c r="D6" t="n">
-        <v>35.423573</v>
+        <v>35.884176</v>
       </c>
       <c r="E6" t="n">
-        <v>64.722156</v>
+        <v>64.677241</v>
       </c>
       <c r="F6" t="n">
-        <v>0.577947</v>
+        <v>0.578532</v>
       </c>
     </row>
     <row r="7">
@@ -4141,16 +4135,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>35.182884</v>
+        <v>35.505143</v>
       </c>
       <c r="D7" t="n">
-        <v>36.026658</v>
+        <v>36.179734</v>
       </c>
       <c r="E7" t="n">
-        <v>63.529348</v>
+        <v>63.504338</v>
       </c>
       <c r="F7" t="n">
-        <v>0.59336</v>
+        <v>0.59368</v>
       </c>
     </row>
     <row r="8">
@@ -4163,16 +4157,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>35.407767</v>
+        <v>35.549074</v>
       </c>
       <c r="D8" t="n">
-        <v>34.688367</v>
+        <v>35.101361</v>
       </c>
       <c r="E8" t="n">
-        <v>59.132984</v>
+        <v>59.80829</v>
       </c>
       <c r="F8" t="n">
-        <v>0.69186</v>
+        <v>0.684782</v>
       </c>
     </row>
     <row r="9">
@@ -4185,16 +4179,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>36.189409</v>
+        <v>35.993351</v>
       </c>
       <c r="D9" t="n">
-        <v>35.762937</v>
+        <v>35.684738</v>
       </c>
       <c r="E9" t="n">
-        <v>60.205093</v>
+        <v>59.764083</v>
       </c>
       <c r="F9" t="n">
-        <v>0.680585</v>
+        <v>0.6852470000000001</v>
       </c>
     </row>
     <row r="10">
@@ -4207,16 +4201,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>37.379754</v>
+        <v>37.198006</v>
       </c>
       <c r="D10" t="n">
-        <v>36.375737</v>
+        <v>36.313587</v>
       </c>
       <c r="E10" t="n">
-        <v>68.037413</v>
+        <v>67.662936</v>
       </c>
       <c r="F10" t="n">
-        <v>0.552131</v>
+        <v>0.557048</v>
       </c>
     </row>
     <row r="11">
@@ -4229,16 +4223,16 @@
         </is>
       </c>
       <c r="C11" t="n">
-        <v>38.486587</v>
+        <v>38.494746</v>
       </c>
       <c r="D11" t="n">
-        <v>36.442314</v>
+        <v>36.696483</v>
       </c>
       <c r="E11" t="n">
-        <v>66.422023</v>
+        <v>68.182388</v>
       </c>
       <c r="F11" t="n">
-        <v>0.573146</v>
+        <v>0.550221</v>
       </c>
     </row>
   </sheetData>
@@ -4289,16 +4283,16 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>36.529528</v>
+        <v>36.566702</v>
       </c>
       <c r="C2" t="n">
-        <v>1.224146</v>
+        <v>1.185831</v>
       </c>
       <c r="D2" t="n">
-        <v>36.220616</v>
+        <v>36.360625</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3147</v>
+        <v>0.429612</v>
       </c>
     </row>
     <row r="3">
@@ -4308,16 +4302,16 @@
         </is>
       </c>
       <c r="B3" t="n">
-        <v>35.752425</v>
+        <v>35.544813</v>
       </c>
       <c r="C3" t="n">
-        <v>1.243333</v>
+        <v>1.164656</v>
       </c>
       <c r="D3" t="n">
-        <v>35.603229</v>
+        <v>35.725168</v>
       </c>
       <c r="E3" t="n">
-        <v>0.785393</v>
+        <v>0.497554</v>
       </c>
     </row>
   </sheetData>
